--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/23,07,26 ПОКОМ КИ/дв 23,07,26 млрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/23,07,26 ПОКОМ КИ/дв 23,07,26 млрсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\23,07,26 ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\23,07,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C1656F-2795-49CB-814B-2517CE0F6208}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33BD4434-BC1E-4C6D-8BE7-4CB645140CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,15 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AL$132</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -696,7 +688,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -710,7 +702,6 @@
     <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
@@ -1032,9 +1023,10 @@
     <col min="15" max="24" width="7" customWidth="1"/>
     <col min="25" max="26" width="5" customWidth="1"/>
     <col min="27" max="36" width="6" customWidth="1"/>
-    <col min="37" max="37" width="31.140625" customWidth="1"/>
+    <col min="37" max="37" width="23.85546875" customWidth="1"/>
     <col min="38" max="38" width="7" customWidth="1"/>
-    <col min="39" max="48" width="3" customWidth="1"/>
+    <col min="39" max="39" width="9" customWidth="1"/>
+    <col min="40" max="48" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:48" x14ac:dyDescent="0.25">
@@ -1061,7 +1053,7 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
-      <c r="X1" s="15">
+      <c r="X1" s="14">
         <v>-1</v>
       </c>
       <c r="Y1" s="1"/>
@@ -1592,7 +1584,10 @@
         <f>ROUND(G6*X6,0)</f>
         <v>62</v>
       </c>
-      <c r="AM6" s="1"/>
+      <c r="AM6" s="1">
+        <f>(SUM(AA6:AJ6)+V6)/11*7</f>
+        <v>448.71260000000007</v>
+      </c>
       <c r="AN6" s="1"/>
       <c r="AO6" s="1"/>
       <c r="AP6" s="1"/>
@@ -1713,7 +1708,10 @@
         <f t="shared" ref="AL7:AL70" si="7">ROUND(G7*X7,0)</f>
         <v>948</v>
       </c>
-      <c r="AM7" s="1"/>
+      <c r="AM7" s="1">
+        <f t="shared" ref="AM7:AM70" si="8">(SUM(AA7:AJ7)+V7)/11*7</f>
+        <v>988.26827272727269</v>
+      </c>
       <c r="AN7" s="1"/>
       <c r="AO7" s="1"/>
       <c r="AP7" s="1"/>
@@ -1834,7 +1832,10 @@
         <f t="shared" si="7"/>
         <v>993</v>
       </c>
-      <c r="AM8" s="1"/>
+      <c r="AM8" s="1">
+        <f t="shared" si="8"/>
+        <v>944.58827272727285</v>
+      </c>
       <c r="AN8" s="1"/>
       <c r="AO8" s="1"/>
       <c r="AP8" s="1"/>
@@ -1900,7 +1901,7 @@
         <v>25</v>
       </c>
       <c r="X9" s="5">
-        <f t="shared" ref="X9:X70" si="8">W9</f>
+        <f t="shared" ref="X9:X70" si="9">W9</f>
         <v>25</v>
       </c>
       <c r="Y9" s="1">
@@ -1948,7 +1949,10 @@
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="AM9" s="1"/>
+      <c r="AM9" s="1">
+        <f t="shared" si="8"/>
+        <v>7.1272727272727279</v>
+      </c>
       <c r="AN9" s="1"/>
       <c r="AO9" s="1"/>
       <c r="AP9" s="1"/>
@@ -2023,7 +2027,7 @@
         <v>546.4000000000002</v>
       </c>
       <c r="X10" s="5">
-        <f t="shared" ref="X10:X11" si="9">W10+$X$1*V10</f>
+        <f t="shared" ref="X10:X11" si="10">W10+$X$1*V10</f>
         <v>469.4000000000002</v>
       </c>
       <c r="Y10" s="1">
@@ -2069,7 +2073,10 @@
         <f t="shared" si="7"/>
         <v>211</v>
       </c>
-      <c r="AM10" s="1"/>
+      <c r="AM10" s="1">
+        <f t="shared" si="8"/>
+        <v>440.10909090909092</v>
+      </c>
       <c r="AN10" s="1"/>
       <c r="AO10" s="1"/>
       <c r="AP10" s="1"/>
@@ -2144,7 +2151,7 @@
         <v>622.51999999999975</v>
       </c>
       <c r="X11" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>528.7199999999998</v>
       </c>
       <c r="Y11" s="1">
@@ -2190,7 +2197,10 @@
         <f t="shared" si="7"/>
         <v>238</v>
       </c>
-      <c r="AM11" s="1"/>
+      <c r="AM11" s="1">
+        <f t="shared" si="8"/>
+        <v>552.49090909090899</v>
+      </c>
       <c r="AN11" s="1"/>
       <c r="AO11" s="1"/>
       <c r="AP11" s="1"/>
@@ -2242,7 +2252,7 @@
       </c>
       <c r="W12" s="12"/>
       <c r="X12" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y12" s="1" t="e">
@@ -2290,7 +2300,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM12" s="1"/>
+      <c r="AM12" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AN12" s="1"/>
       <c r="AO12" s="1"/>
       <c r="AP12" s="1"/>
@@ -2355,11 +2368,11 @@
         <v>23</v>
       </c>
       <c r="W13" s="5">
-        <f t="shared" ref="W13:W24" si="10">12*V13-U13-T13-S13-R13-Q13-P13-O13-F13</f>
+        <f t="shared" ref="W13:W24" si="11">12*V13-U13-T13-S13-R13-Q13-P13-O13-F13</f>
         <v>116</v>
       </c>
       <c r="X13" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>116</v>
       </c>
       <c r="Y13" s="1">
@@ -2405,7 +2418,10 @@
         <f t="shared" si="7"/>
         <v>35</v>
       </c>
-      <c r="AM13" s="1"/>
+      <c r="AM13" s="1">
+        <f t="shared" si="8"/>
+        <v>122.30909090909091</v>
+      </c>
       <c r="AN13" s="1"/>
       <c r="AO13" s="1"/>
       <c r="AP13" s="1"/>
@@ -2471,7 +2487,7 @@
       </c>
       <c r="W14" s="5"/>
       <c r="X14" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y14" s="1">
@@ -2519,7 +2535,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM14" s="1"/>
+      <c r="AM14" s="1">
+        <f t="shared" si="8"/>
+        <v>158.07272727272726</v>
+      </c>
       <c r="AN14" s="1"/>
       <c r="AO14" s="1"/>
       <c r="AP14" s="1"/>
@@ -2586,11 +2605,11 @@
         <v>83.318399999999997</v>
       </c>
       <c r="W15" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>87.607600000000105</v>
       </c>
       <c r="X15" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>87.607600000000105</v>
       </c>
       <c r="Y15" s="1">
@@ -2636,7 +2655,10 @@
         <f t="shared" si="7"/>
         <v>88</v>
       </c>
-      <c r="AM15" s="1"/>
+      <c r="AM15" s="1">
+        <f t="shared" si="8"/>
+        <v>487.35094545454541</v>
+      </c>
       <c r="AN15" s="1"/>
       <c r="AO15" s="1"/>
       <c r="AP15" s="1"/>
@@ -2757,7 +2779,10 @@
         <f t="shared" si="7"/>
         <v>2551</v>
       </c>
-      <c r="AM16" s="1"/>
+      <c r="AM16" s="1">
+        <f t="shared" si="8"/>
+        <v>2431.4394363636366</v>
+      </c>
       <c r="AN16" s="1"/>
       <c r="AO16" s="1"/>
       <c r="AP16" s="1"/>
@@ -2822,11 +2847,11 @@
         <v>22.732400000000002</v>
       </c>
       <c r="W17" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>129.92720000000006</v>
       </c>
       <c r="X17" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>129.92720000000006</v>
       </c>
       <c r="Y17" s="1">
@@ -2872,7 +2897,10 @@
         <f t="shared" si="7"/>
         <v>130</v>
       </c>
-      <c r="AM17" s="1"/>
+      <c r="AM17" s="1">
+        <f t="shared" si="8"/>
+        <v>122.59749090909091</v>
+      </c>
       <c r="AN17" s="1"/>
       <c r="AO17" s="1"/>
       <c r="AP17" s="1"/>
@@ -2935,11 +2963,11 @@
         <v>10.711600000000001</v>
       </c>
       <c r="W18" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>29.437199999999997</v>
       </c>
       <c r="X18" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>29.437199999999997</v>
       </c>
       <c r="Y18" s="1">
@@ -2985,7 +3013,10 @@
         <f t="shared" si="7"/>
         <v>29</v>
       </c>
-      <c r="AM18" s="1"/>
+      <c r="AM18" s="1">
+        <f t="shared" si="8"/>
+        <v>52.055690909090906</v>
+      </c>
       <c r="AN18" s="1"/>
       <c r="AO18" s="1"/>
       <c r="AP18" s="1"/>
@@ -3051,7 +3082,7 @@
       </c>
       <c r="W19" s="5"/>
       <c r="X19" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y19" s="1">
@@ -3097,7 +3128,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM19" s="1"/>
+      <c r="AM19" s="1">
+        <f t="shared" si="8"/>
+        <v>25.442709090909091</v>
+      </c>
       <c r="AN19" s="1"/>
       <c r="AO19" s="1"/>
       <c r="AP19" s="1"/>
@@ -3164,11 +3198,11 @@
         <v>99.254800000000003</v>
       </c>
       <c r="W20" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>107.21665999999993</v>
       </c>
       <c r="X20" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>107.21665999999993</v>
       </c>
       <c r="Y20" s="1">
@@ -3214,7 +3248,10 @@
         <f t="shared" si="7"/>
         <v>107</v>
       </c>
-      <c r="AM20" s="1"/>
+      <c r="AM20" s="1">
+        <f t="shared" si="8"/>
+        <v>741.98599999999999</v>
+      </c>
       <c r="AN20" s="1"/>
       <c r="AO20" s="1"/>
       <c r="AP20" s="1"/>
@@ -3279,11 +3316,11 @@
         <v>22.8048</v>
       </c>
       <c r="W21" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>144.39349999999999</v>
       </c>
       <c r="X21" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>144.39349999999999</v>
       </c>
       <c r="Y21" s="1">
@@ -3329,7 +3366,10 @@
         <f t="shared" si="7"/>
         <v>144</v>
       </c>
-      <c r="AM21" s="1"/>
+      <c r="AM21" s="1">
+        <f t="shared" si="8"/>
+        <v>121.86669090909092</v>
+      </c>
       <c r="AN21" s="1"/>
       <c r="AO21" s="1"/>
       <c r="AP21" s="1"/>
@@ -3396,11 +3436,11 @@
         <v>57.740400000000001</v>
       </c>
       <c r="W22" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>107.94980000000004</v>
       </c>
       <c r="X22" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>107.94980000000004</v>
       </c>
       <c r="Y22" s="1">
@@ -3446,7 +3486,10 @@
         <f t="shared" si="7"/>
         <v>108</v>
       </c>
-      <c r="AM22" s="1"/>
+      <c r="AM22" s="1">
+        <f t="shared" si="8"/>
+        <v>352.6972909090909</v>
+      </c>
       <c r="AN22" s="1"/>
       <c r="AO22" s="1"/>
       <c r="AP22" s="1"/>
@@ -3511,11 +3554,11 @@
         <v>3.0114000000000001</v>
       </c>
       <c r="W23" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.2607999999999997</v>
       </c>
       <c r="X23" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6.2607999999999997</v>
       </c>
       <c r="Y23" s="1">
@@ -3561,7 +3604,10 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="AM23" s="1"/>
+      <c r="AM23" s="1">
+        <f t="shared" si="8"/>
+        <v>22.776472727272726</v>
+      </c>
       <c r="AN23" s="1"/>
       <c r="AO23" s="1"/>
       <c r="AP23" s="1"/>
@@ -3628,11 +3674,11 @@
         <v>51.419200000000004</v>
       </c>
       <c r="W24" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>154.52079999999989</v>
       </c>
       <c r="X24" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>154.52079999999989</v>
       </c>
       <c r="Y24" s="1">
@@ -3678,7 +3724,10 @@
         <f t="shared" si="7"/>
         <v>155</v>
       </c>
-      <c r="AM24" s="1"/>
+      <c r="AM24" s="1">
+        <f t="shared" si="8"/>
+        <v>371.5992</v>
+      </c>
       <c r="AN24" s="1"/>
       <c r="AO24" s="1"/>
       <c r="AP24" s="1"/>
@@ -3744,7 +3793,7 @@
       </c>
       <c r="W25" s="12"/>
       <c r="X25" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y25" s="1">
@@ -3790,7 +3839,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM25" s="1"/>
+      <c r="AM25" s="1">
+        <f t="shared" si="8"/>
+        <v>30.895327272727272</v>
+      </c>
       <c r="AN25" s="1"/>
       <c r="AO25" s="1"/>
       <c r="AP25" s="1"/>
@@ -3842,7 +3894,7 @@
       </c>
       <c r="W26" s="12"/>
       <c r="X26" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y26" s="1" t="e">
@@ -3890,7 +3942,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM26" s="1"/>
+      <c r="AM26" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1"/>
       <c r="AP26" s="1"/>
@@ -3957,11 +4012,11 @@
         <v>34.602600000000002</v>
       </c>
       <c r="W27" s="5">
-        <f t="shared" ref="W27:W33" si="11">12*V27-U27-T27-S27-R27-Q27-P27-O27-F27</f>
+        <f t="shared" ref="W27:W33" si="12">12*V27-U27-T27-S27-R27-Q27-P27-O27-F27</f>
         <v>164.14400000000006</v>
       </c>
       <c r="X27" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>164.14400000000006</v>
       </c>
       <c r="Y27" s="1">
@@ -4007,7 +4062,10 @@
         <f t="shared" si="7"/>
         <v>164</v>
       </c>
-      <c r="AM27" s="1"/>
+      <c r="AM27" s="1">
+        <f t="shared" si="8"/>
+        <v>172.38199999999998</v>
+      </c>
       <c r="AN27" s="1"/>
       <c r="AO27" s="1"/>
       <c r="AP27" s="1"/>
@@ -4078,11 +4136,11 @@
         <v>66.114800000000002</v>
       </c>
       <c r="W28" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>291.36843999999991</v>
       </c>
       <c r="X28" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>291.36843999999991</v>
       </c>
       <c r="Y28" s="1">
@@ -4128,7 +4186,10 @@
         <f t="shared" si="7"/>
         <v>291</v>
       </c>
-      <c r="AM28" s="1"/>
+      <c r="AM28" s="1">
+        <f t="shared" si="8"/>
+        <v>445.48521818181814</v>
+      </c>
       <c r="AN28" s="1"/>
       <c r="AO28" s="1"/>
       <c r="AP28" s="1"/>
@@ -4199,11 +4260,11 @@
         <v>51.875800000000005</v>
       </c>
       <c r="W29" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>160.29017000000027</v>
       </c>
       <c r="X29" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>160.29017000000027</v>
       </c>
       <c r="Y29" s="1">
@@ -4249,7 +4310,10 @@
         <f t="shared" si="7"/>
         <v>160</v>
       </c>
-      <c r="AM29" s="1"/>
+      <c r="AM29" s="1">
+        <f t="shared" si="8"/>
+        <v>455.30176363636372</v>
+      </c>
       <c r="AN29" s="1"/>
       <c r="AO29" s="1"/>
       <c r="AP29" s="1"/>
@@ -4370,7 +4434,10 @@
         <f t="shared" si="7"/>
         <v>1097</v>
       </c>
-      <c r="AM30" s="1"/>
+      <c r="AM30" s="1">
+        <f t="shared" si="8"/>
+        <v>982.78230909090894</v>
+      </c>
       <c r="AN30" s="1"/>
       <c r="AO30" s="1"/>
       <c r="AP30" s="1"/>
@@ -4438,7 +4505,7 @@
       </c>
       <c r="W31" s="5"/>
       <c r="X31" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y31" s="1">
@@ -4484,7 +4551,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM31" s="1"/>
+      <c r="AM31" s="1">
+        <f t="shared" si="8"/>
+        <v>34.268945454545459</v>
+      </c>
       <c r="AN31" s="1"/>
       <c r="AO31" s="1"/>
       <c r="AP31" s="1"/>
@@ -4555,7 +4625,7 @@
         <v>76.444800000000015</v>
       </c>
       <c r="X32" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>76.444800000000015</v>
       </c>
       <c r="Y32" s="1">
@@ -4601,7 +4671,10 @@
         <f t="shared" si="7"/>
         <v>76</v>
       </c>
-      <c r="AM32" s="1"/>
+      <c r="AM32" s="1">
+        <f t="shared" si="8"/>
+        <v>68.029181818181797</v>
+      </c>
       <c r="AN32" s="1"/>
       <c r="AO32" s="1"/>
       <c r="AP32" s="1"/>
@@ -4666,11 +4739,11 @@
         <v>13.867599999999999</v>
       </c>
       <c r="W33" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>24.616600000000005</v>
       </c>
       <c r="X33" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>24.616600000000005</v>
       </c>
       <c r="Y33" s="1">
@@ -4716,7 +4789,10 @@
         <f t="shared" si="7"/>
         <v>25</v>
       </c>
-      <c r="AM33" s="1"/>
+      <c r="AM33" s="1">
+        <f t="shared" si="8"/>
+        <v>99.571054545454572</v>
+      </c>
       <c r="AN33" s="1"/>
       <c r="AO33" s="1"/>
       <c r="AP33" s="1"/>
@@ -4782,7 +4858,7 @@
       </c>
       <c r="W34" s="12"/>
       <c r="X34" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y34" s="1">
@@ -4828,7 +4904,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM34" s="1"/>
+      <c r="AM34" s="1">
+        <f t="shared" si="8"/>
+        <v>65.158545454545447</v>
+      </c>
       <c r="AN34" s="1"/>
       <c r="AO34" s="1"/>
       <c r="AP34" s="1"/>
@@ -4893,11 +4972,11 @@
         <v>12.270399999999999</v>
       </c>
       <c r="W35" s="5">
-        <f t="shared" ref="W35:W43" si="12">12*V35-U35-T35-S35-R35-Q35-P35-O35-F35</f>
+        <f t="shared" ref="W35:W43" si="13">12*V35-U35-T35-S35-R35-Q35-P35-O35-F35</f>
         <v>58.607399999999984</v>
       </c>
       <c r="X35" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>58.607399999999984</v>
       </c>
       <c r="Y35" s="1">
@@ -4943,7 +5022,10 @@
         <f t="shared" si="7"/>
         <v>59</v>
       </c>
-      <c r="AM35" s="1"/>
+      <c r="AM35" s="1">
+        <f t="shared" si="8"/>
+        <v>58.097454545454539</v>
+      </c>
       <c r="AN35" s="1"/>
       <c r="AO35" s="1"/>
       <c r="AP35" s="1"/>
@@ -5012,11 +5094,11 @@
         <v>260</v>
       </c>
       <c r="W36" s="5">
-        <f t="shared" ref="W36:W38" si="13">11*V36-U36-T36-S36-R36-Q36-P36-O36-F36</f>
+        <f t="shared" ref="W36:W38" si="14">11*V36-U36-T36-S36-R36-Q36-P36-O36-F36</f>
         <v>1713.5780000000002</v>
       </c>
       <c r="X36" s="5">
-        <f t="shared" ref="X36:X38" si="14">W36+$X$1*V36</f>
+        <f t="shared" ref="X36:X38" si="15">W36+$X$1*V36</f>
         <v>1453.5780000000002</v>
       </c>
       <c r="Y36" s="1">
@@ -5062,7 +5144,10 @@
         <f t="shared" si="7"/>
         <v>581</v>
       </c>
-      <c r="AM36" s="1"/>
+      <c r="AM36" s="1">
+        <f t="shared" si="8"/>
+        <v>1537.149090909091</v>
+      </c>
       <c r="AN36" s="1"/>
       <c r="AO36" s="1"/>
       <c r="AP36" s="1"/>
@@ -5129,11 +5214,11 @@
         <v>71</v>
       </c>
       <c r="W37" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>521.4</v>
       </c>
       <c r="X37" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>450.4</v>
       </c>
       <c r="Y37" s="1">
@@ -5179,7 +5264,10 @@
         <f t="shared" si="7"/>
         <v>203</v>
       </c>
-      <c r="AM37" s="1"/>
+      <c r="AM37" s="1">
+        <f t="shared" si="8"/>
+        <v>336.50909090909096</v>
+      </c>
       <c r="AN37" s="1"/>
       <c r="AO37" s="1"/>
       <c r="AP37" s="1"/>
@@ -5223,7 +5311,7 @@
         <v>457</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="15">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="16">E38-K38</f>
         <v>-142</v>
       </c>
       <c r="M38" s="1"/>
@@ -5246,11 +5334,11 @@
         <v>63</v>
       </c>
       <c r="W38" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>414.91999999999979</v>
       </c>
       <c r="X38" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>351.91999999999979</v>
       </c>
       <c r="Y38" s="1">
@@ -5296,7 +5384,10 @@
         <f t="shared" si="7"/>
         <v>141</v>
       </c>
-      <c r="AM38" s="1"/>
+      <c r="AM38" s="1">
+        <f t="shared" si="8"/>
+        <v>422.67272727272729</v>
+      </c>
       <c r="AN38" s="1"/>
       <c r="AO38" s="1"/>
       <c r="AP38" s="1"/>
@@ -5338,7 +5429,7 @@
         <v>68</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="M39" s="1"/>
@@ -5365,7 +5456,7 @@
         <v>106.20000000000002</v>
       </c>
       <c r="X39" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>106.20000000000002</v>
       </c>
       <c r="Y39" s="1">
@@ -5411,7 +5502,10 @@
         <f t="shared" si="7"/>
         <v>42</v>
       </c>
-      <c r="AM39" s="1"/>
+      <c r="AM39" s="1">
+        <f t="shared" si="8"/>
+        <v>59.181818181818187</v>
+      </c>
       <c r="AN39" s="1"/>
       <c r="AO39" s="1"/>
       <c r="AP39" s="1"/>
@@ -5453,7 +5547,7 @@
         <v>23</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.15599999999999881</v>
       </c>
       <c r="M40" s="1"/>
@@ -5474,11 +5568,11 @@
         <v>4.6311999999999998</v>
       </c>
       <c r="W40" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>29.595399999999998</v>
       </c>
       <c r="X40" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>29.595399999999998</v>
       </c>
       <c r="Y40" s="1">
@@ -5524,7 +5618,10 @@
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
-      <c r="AM40" s="1"/>
+      <c r="AM40" s="1">
+        <f t="shared" si="8"/>
+        <v>16.358109090909092</v>
+      </c>
       <c r="AN40" s="1"/>
       <c r="AO40" s="1"/>
       <c r="AP40" s="1"/>
@@ -5568,7 +5665,7 @@
         <v>237</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>96</v>
       </c>
       <c r="M41" s="1"/>
@@ -5591,11 +5688,11 @@
         <v>66.599999999999994</v>
       </c>
       <c r="W41" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>282.79999999999984</v>
       </c>
       <c r="X41" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>282.79999999999984</v>
       </c>
       <c r="Y41" s="1">
@@ -5641,7 +5738,10 @@
         <f t="shared" si="7"/>
         <v>28</v>
       </c>
-      <c r="AM41" s="1"/>
+      <c r="AM41" s="1">
+        <f t="shared" si="8"/>
+        <v>390.21818181818179</v>
+      </c>
       <c r="AN41" s="1"/>
       <c r="AO41" s="1"/>
       <c r="AP41" s="1"/>
@@ -5685,7 +5785,7 @@
         <v>296</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-30</v>
       </c>
       <c r="M42" s="1"/>
@@ -5708,11 +5808,11 @@
         <v>53.2</v>
       </c>
       <c r="W42" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>289.40000000000009</v>
       </c>
       <c r="X42" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>289.40000000000009</v>
       </c>
       <c r="Y42" s="1">
@@ -5758,7 +5858,10 @@
         <f t="shared" si="7"/>
         <v>101</v>
       </c>
-      <c r="AM42" s="1"/>
+      <c r="AM42" s="1">
+        <f t="shared" si="8"/>
+        <v>215.34545454545454</v>
+      </c>
       <c r="AN42" s="1"/>
       <c r="AO42" s="1"/>
       <c r="AP42" s="1"/>
@@ -5802,7 +5905,7 @@
         <v>132.6</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-3.5190000000000055</v>
       </c>
       <c r="M43" s="1"/>
@@ -5823,11 +5926,11 @@
         <v>25.816199999999998</v>
       </c>
       <c r="W43" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>101.78039999999999</v>
       </c>
       <c r="X43" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>101.78039999999999</v>
       </c>
       <c r="Y43" s="1">
@@ -5873,7 +5976,10 @@
         <f t="shared" si="7"/>
         <v>102</v>
       </c>
-      <c r="AM43" s="1"/>
+      <c r="AM43" s="1">
+        <f t="shared" si="8"/>
+        <v>125.51470909090909</v>
+      </c>
       <c r="AN43" s="1"/>
       <c r="AO43" s="1"/>
       <c r="AP43" s="1"/>
@@ -5917,7 +6023,7 @@
         <v>166</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-158</v>
       </c>
       <c r="M44" s="1"/>
@@ -5941,7 +6047,7 @@
         <v>100</v>
       </c>
       <c r="X44" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
       <c r="Y44" s="1">
@@ -5987,7 +6093,10 @@
         <f t="shared" si="7"/>
         <v>40</v>
       </c>
-      <c r="AM44" s="1"/>
+      <c r="AM44" s="1">
+        <f t="shared" si="8"/>
+        <v>147.36909090909091</v>
+      </c>
       <c r="AN44" s="1"/>
       <c r="AO44" s="1"/>
       <c r="AP44" s="1"/>
@@ -6031,7 +6140,7 @@
         <v>219</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-31</v>
       </c>
       <c r="M45" s="1"/>
@@ -6062,7 +6171,7 @@
         <v>253.20000000000005</v>
       </c>
       <c r="X45" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>253.20000000000005</v>
       </c>
       <c r="Y45" s="1">
@@ -6108,7 +6217,10 @@
         <f t="shared" si="7"/>
         <v>101</v>
       </c>
-      <c r="AM45" s="1"/>
+      <c r="AM45" s="1">
+        <f t="shared" si="8"/>
+        <v>188.3636363636364</v>
+      </c>
       <c r="AN45" s="1"/>
       <c r="AO45" s="1"/>
       <c r="AP45" s="1"/>
@@ -6152,7 +6264,7 @@
         <v>76.5</v>
       </c>
       <c r="L46" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-3.3070000000000022</v>
       </c>
       <c r="M46" s="10"/>
@@ -6174,7 +6286,7 @@
       </c>
       <c r="W46" s="12"/>
       <c r="X46" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y46" s="1">
@@ -6220,7 +6332,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM46" s="1"/>
+      <c r="AM46" s="1">
+        <f t="shared" si="8"/>
+        <v>65.275254545454544</v>
+      </c>
       <c r="AN46" s="1"/>
       <c r="AO46" s="1"/>
       <c r="AP46" s="1"/>
@@ -6264,7 +6379,7 @@
         <v>160.4</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.561000000000007</v>
       </c>
       <c r="M47" s="1"/>
@@ -6287,11 +6402,11 @@
         <v>32.792200000000001</v>
       </c>
       <c r="W47" s="5">
-        <f t="shared" ref="W47:W70" si="16">12*V47-U47-T47-S47-R47-Q47-P47-O47-F47</f>
+        <f t="shared" ref="W47:W70" si="17">12*V47-U47-T47-S47-R47-Q47-P47-O47-F47</f>
         <v>145.78280000000001</v>
       </c>
       <c r="X47" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>145.78280000000001</v>
       </c>
       <c r="Y47" s="1">
@@ -6337,7 +6452,10 @@
         <f t="shared" si="7"/>
         <v>146</v>
       </c>
-      <c r="AM47" s="1"/>
+      <c r="AM47" s="1">
+        <f t="shared" si="8"/>
+        <v>154.59118181818181</v>
+      </c>
       <c r="AN47" s="1"/>
       <c r="AO47" s="1"/>
       <c r="AP47" s="1"/>
@@ -6381,7 +6499,7 @@
         <v>503</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-1</v>
       </c>
       <c r="M48" s="1"/>
@@ -6412,7 +6530,7 @@
         <v>666.11999999999989</v>
       </c>
       <c r="X48" s="5">
-        <f t="shared" ref="X48:X49" si="17">W48+$X$1*V48</f>
+        <f t="shared" ref="X48:X49" si="18">W48+$X$1*V48</f>
         <v>565.71999999999991</v>
       </c>
       <c r="Y48" s="1">
@@ -6458,7 +6576,10 @@
         <f t="shared" si="7"/>
         <v>198</v>
       </c>
-      <c r="AM48" s="1"/>
+      <c r="AM48" s="1">
+        <f t="shared" si="8"/>
+        <v>508.04727272727274</v>
+      </c>
       <c r="AN48" s="1"/>
       <c r="AO48" s="1"/>
       <c r="AP48" s="1"/>
@@ -6502,7 +6623,7 @@
         <v>505</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-103</v>
       </c>
       <c r="M49" s="1"/>
@@ -6527,7 +6648,7 @@
         <v>556.80000000000007</v>
       </c>
       <c r="X49" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>476.40000000000009</v>
       </c>
       <c r="Y49" s="1">
@@ -6573,7 +6694,10 @@
         <f t="shared" si="7"/>
         <v>191</v>
       </c>
-      <c r="AM49" s="1"/>
+      <c r="AM49" s="1">
+        <f t="shared" si="8"/>
+        <v>362.85454545454547</v>
+      </c>
       <c r="AN49" s="1"/>
       <c r="AO49" s="1"/>
       <c r="AP49" s="1"/>
@@ -6617,7 +6741,7 @@
         <v>34</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.65599999999999881</v>
       </c>
       <c r="M50" s="1"/>
@@ -6638,11 +6762,11 @@
         <v>6.9311999999999996</v>
       </c>
       <c r="W50" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>9.9443999999999875</v>
       </c>
       <c r="X50" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.9443999999999875</v>
       </c>
       <c r="Y50" s="1">
@@ -6688,7 +6812,10 @@
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="AM50" s="1"/>
+      <c r="AM50" s="1">
+        <f t="shared" si="8"/>
+        <v>45.885763636363635</v>
+      </c>
       <c r="AN50" s="1"/>
       <c r="AO50" s="1"/>
       <c r="AP50" s="1"/>
@@ -6732,7 +6859,7 @@
         <v>84.7</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.796999999999997</v>
       </c>
       <c r="M51" s="1"/>
@@ -6756,7 +6883,7 @@
       </c>
       <c r="W51" s="5"/>
       <c r="X51" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y51" s="1">
@@ -6804,7 +6931,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM51" s="1"/>
+      <c r="AM51" s="1">
+        <f t="shared" si="8"/>
+        <v>163.4864</v>
+      </c>
       <c r="AN51" s="1"/>
       <c r="AO51" s="1"/>
       <c r="AP51" s="1"/>
@@ -6848,7 +6978,7 @@
         <v>171.7</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-88.572999999999993</v>
       </c>
       <c r="M52" s="1"/>
@@ -6873,7 +7003,7 @@
         <v>120.22999999999999</v>
       </c>
       <c r="X52" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>120.22999999999999</v>
       </c>
       <c r="Y52" s="1">
@@ -6919,7 +7049,10 @@
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="AM52" s="1"/>
+      <c r="AM52" s="1">
+        <f t="shared" si="8"/>
+        <v>44.398709090909087</v>
+      </c>
       <c r="AN52" s="1"/>
       <c r="AO52" s="1"/>
       <c r="AP52" s="1"/>
@@ -6963,7 +7096,7 @@
         <v>218</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-63</v>
       </c>
       <c r="M53" s="1"/>
@@ -6986,11 +7119,11 @@
         <v>31</v>
       </c>
       <c r="W53" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>101.39999999999999</v>
       </c>
       <c r="X53" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>101.39999999999999</v>
       </c>
       <c r="Y53" s="1">
@@ -7036,7 +7169,10 @@
         <f t="shared" si="7"/>
         <v>46</v>
       </c>
-      <c r="AM53" s="1"/>
+      <c r="AM53" s="1">
+        <f t="shared" si="8"/>
+        <v>180.59999999999997</v>
+      </c>
       <c r="AN53" s="1"/>
       <c r="AO53" s="1"/>
       <c r="AP53" s="1"/>
@@ -7080,7 +7216,7 @@
         <v>203</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-1</v>
       </c>
       <c r="M54" s="1"/>
@@ -7101,11 +7237,11 @@
         <v>40.4</v>
       </c>
       <c r="W54" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>259.79999999999995</v>
       </c>
       <c r="X54" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>259.79999999999995</v>
       </c>
       <c r="Y54" s="1">
@@ -7151,7 +7287,10 @@
         <f t="shared" si="7"/>
         <v>117</v>
       </c>
-      <c r="AM54" s="1"/>
+      <c r="AM54" s="1">
+        <f t="shared" si="8"/>
+        <v>276.81818181818176</v>
+      </c>
       <c r="AN54" s="1"/>
       <c r="AO54" s="1"/>
       <c r="AP54" s="1"/>
@@ -7195,7 +7334,7 @@
         <v>167</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-4</v>
       </c>
       <c r="M55" s="1"/>
@@ -7224,7 +7363,7 @@
         <v>222.2</v>
       </c>
       <c r="X55" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>222.2</v>
       </c>
       <c r="Y55" s="1">
@@ -7270,7 +7409,10 @@
         <f t="shared" si="7"/>
         <v>89</v>
       </c>
-      <c r="AM55" s="1"/>
+      <c r="AM55" s="1">
+        <f t="shared" si="8"/>
+        <v>121.2909090909091</v>
+      </c>
       <c r="AN55" s="1"/>
       <c r="AO55" s="1"/>
       <c r="AP55" s="1"/>
@@ -7312,7 +7454,7 @@
         <v>162</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-4</v>
       </c>
       <c r="M56" s="1"/>
@@ -7343,7 +7485,7 @@
         <v>215.00000000000006</v>
       </c>
       <c r="X56" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>215.00000000000006</v>
       </c>
       <c r="Y56" s="1">
@@ -7389,7 +7531,10 @@
         <f t="shared" si="7"/>
         <v>86</v>
       </c>
-      <c r="AM56" s="1"/>
+      <c r="AM56" s="1">
+        <f t="shared" si="8"/>
+        <v>89.345454545454544</v>
+      </c>
       <c r="AN56" s="1"/>
       <c r="AO56" s="1"/>
       <c r="AP56" s="1"/>
@@ -7433,7 +7578,7 @@
         <v>92.25</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.0100000000000051</v>
       </c>
       <c r="M57" s="1"/>
@@ -7456,11 +7601,11 @@
         <v>18.852</v>
       </c>
       <c r="W57" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>30.144999999999982</v>
       </c>
       <c r="X57" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>30.144999999999982</v>
       </c>
       <c r="Y57" s="1">
@@ -7506,7 +7651,10 @@
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
-      <c r="AM57" s="1"/>
+      <c r="AM57" s="1">
+        <f t="shared" si="8"/>
+        <v>139.45145454545454</v>
+      </c>
       <c r="AN57" s="1"/>
       <c r="AO57" s="1"/>
       <c r="AP57" s="1"/>
@@ -7550,7 +7698,7 @@
         <v>119</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>8</v>
       </c>
       <c r="M58" s="1"/>
@@ -7572,7 +7720,7 @@
       </c>
       <c r="W58" s="5"/>
       <c r="X58" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y58" s="1">
@@ -7618,7 +7766,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM58" s="1"/>
+      <c r="AM58" s="1">
+        <f t="shared" si="8"/>
+        <v>275.54545454545456</v>
+      </c>
       <c r="AN58" s="1"/>
       <c r="AO58" s="1"/>
       <c r="AP58" s="1"/>
@@ -7662,7 +7813,7 @@
         <v>61.4</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.8690000000000069</v>
       </c>
       <c r="M59" s="1"/>
@@ -7684,7 +7835,7 @@
       </c>
       <c r="W59" s="5"/>
       <c r="X59" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y59" s="1">
@@ -7730,7 +7881,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM59" s="1"/>
+      <c r="AM59" s="1">
+        <f t="shared" si="8"/>
+        <v>118.54436363636364</v>
+      </c>
       <c r="AN59" s="1"/>
       <c r="AO59" s="1"/>
       <c r="AP59" s="1"/>
@@ -7774,7 +7928,7 @@
         <v>19.899999999999999</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.32800000000000296</v>
       </c>
       <c r="M60" s="1"/>
@@ -7796,7 +7950,7 @@
       </c>
       <c r="W60" s="5"/>
       <c r="X60" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y60" s="1">
@@ -7842,7 +7996,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM60" s="1"/>
+      <c r="AM60" s="1">
+        <f t="shared" si="8"/>
+        <v>29.238745454545459</v>
+      </c>
       <c r="AN60" s="1"/>
       <c r="AO60" s="1"/>
       <c r="AP60" s="1"/>
@@ -7886,7 +8043,7 @@
         <v>188</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-7</v>
       </c>
       <c r="M61" s="1"/>
@@ -7907,11 +8064,11 @@
         <v>36.200000000000003</v>
       </c>
       <c r="W61" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>235.88</v>
       </c>
       <c r="X61" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>235.88</v>
       </c>
       <c r="Y61" s="1">
@@ -7957,7 +8114,10 @@
         <f t="shared" si="7"/>
         <v>24</v>
       </c>
-      <c r="AM61" s="1"/>
+      <c r="AM61" s="1">
+        <f t="shared" si="8"/>
+        <v>265.74545454545455</v>
+      </c>
       <c r="AN61" s="1"/>
       <c r="AO61" s="1"/>
       <c r="AP61" s="1"/>
@@ -7999,7 +8159,7 @@
         <v>16</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-1</v>
       </c>
       <c r="M62" s="1"/>
@@ -8021,7 +8181,7 @@
       </c>
       <c r="W62" s="5"/>
       <c r="X62" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y62" s="1">
@@ -8067,7 +8227,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM62" s="1"/>
+      <c r="AM62" s="1">
+        <f t="shared" si="8"/>
+        <v>28.763636363636365</v>
+      </c>
       <c r="AN62" s="1"/>
       <c r="AO62" s="1"/>
       <c r="AP62" s="1"/>
@@ -8111,7 +8274,7 @@
         <v>23.2</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-1.3939999999999984</v>
       </c>
       <c r="M63" s="1"/>
@@ -8132,11 +8295,11 @@
         <v>4.3612000000000002</v>
       </c>
       <c r="W63" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>32.209600000000002</v>
       </c>
       <c r="X63" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>32.209600000000002</v>
       </c>
       <c r="Y63" s="1">
@@ -8182,7 +8345,10 @@
         <f t="shared" si="7"/>
         <v>32</v>
       </c>
-      <c r="AM63" s="1"/>
+      <c r="AM63" s="1">
+        <f t="shared" si="8"/>
+        <v>13.249854545454545</v>
+      </c>
       <c r="AN63" s="1"/>
       <c r="AO63" s="1"/>
       <c r="AP63" s="1"/>
@@ -8224,7 +8390,7 @@
         <v>39.1</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-0.375</v>
       </c>
       <c r="M64" s="1"/>
@@ -8246,7 +8412,7 @@
       </c>
       <c r="W64" s="5"/>
       <c r="X64" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y64" s="1">
@@ -8292,7 +8458,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM64" s="1"/>
+      <c r="AM64" s="1">
+        <f t="shared" si="8"/>
+        <v>49.362090909090909</v>
+      </c>
       <c r="AN64" s="1"/>
       <c r="AO64" s="1"/>
       <c r="AP64" s="1"/>
@@ -8336,7 +8505,7 @@
         <v>535</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-216</v>
       </c>
       <c r="M65" s="1"/>
@@ -8363,11 +8532,11 @@
         <v>63.8</v>
       </c>
       <c r="W65" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>412.07999999999959</v>
       </c>
       <c r="X65" s="5">
-        <f t="shared" ref="X65:X66" si="18">W65+$X$1*V65</f>
+        <f t="shared" ref="X65:X66" si="19">W65+$X$1*V65</f>
         <v>348.27999999999957</v>
       </c>
       <c r="Y65" s="1">
@@ -8413,7 +8582,10 @@
         <f t="shared" si="7"/>
         <v>139</v>
       </c>
-      <c r="AM65" s="1"/>
+      <c r="AM65" s="1">
+        <f t="shared" si="8"/>
+        <v>561.39999999999986</v>
+      </c>
       <c r="AN65" s="1"/>
       <c r="AO65" s="1"/>
       <c r="AP65" s="1"/>
@@ -8457,7 +8629,7 @@
         <v>497</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-34</v>
       </c>
       <c r="M66" s="1"/>
@@ -8488,7 +8660,7 @@
         <v>667.2</v>
       </c>
       <c r="X66" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>574.6</v>
       </c>
       <c r="Y66" s="1">
@@ -8534,7 +8706,10 @@
         <f t="shared" si="7"/>
         <v>230</v>
       </c>
-      <c r="AM66" s="1"/>
+      <c r="AM66" s="1">
+        <f t="shared" si="8"/>
+        <v>421.78181818181821</v>
+      </c>
       <c r="AN66" s="1"/>
       <c r="AO66" s="1"/>
       <c r="AP66" s="1"/>
@@ -8578,7 +8753,7 @@
         <v>138.5</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-24.456999999999994</v>
       </c>
       <c r="M67" s="1"/>
@@ -8599,11 +8774,11 @@
         <v>22.808600000000002</v>
       </c>
       <c r="W67" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>19.727200000000039</v>
       </c>
       <c r="X67" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>19.727200000000039</v>
       </c>
       <c r="Y67" s="1">
@@ -8649,7 +8824,10 @@
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="AM67" s="1"/>
+      <c r="AM67" s="1">
+        <f t="shared" si="8"/>
+        <v>173.08174545454543</v>
+      </c>
       <c r="AN67" s="1"/>
       <c r="AO67" s="1"/>
       <c r="AP67" s="1"/>
@@ -8693,7 +8871,7 @@
         <v>156.69999999999999</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>11.792000000000002</v>
       </c>
       <c r="M68" s="1"/>
@@ -8716,11 +8894,11 @@
         <v>33.698399999999999</v>
       </c>
       <c r="W68" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>26.66471999999996</v>
       </c>
       <c r="X68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>26.66471999999996</v>
       </c>
       <c r="Y68" s="1">
@@ -8766,7 +8944,10 @@
         <f t="shared" si="7"/>
         <v>27</v>
       </c>
-      <c r="AM68" s="1"/>
+      <c r="AM68" s="1">
+        <f t="shared" si="8"/>
+        <v>200.77285454545455</v>
+      </c>
       <c r="AN68" s="1"/>
       <c r="AO68" s="1"/>
       <c r="AP68" s="1"/>
@@ -8810,7 +8991,7 @@
         <v>356.01400000000001</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>30.291999999999973</v>
       </c>
       <c r="M69" s="1"/>
@@ -8833,11 +9014,11 @@
         <v>77.261200000000002</v>
       </c>
       <c r="W69" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>131.71640000000014</v>
       </c>
       <c r="X69" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>131.71640000000014</v>
       </c>
       <c r="Y69" s="1">
@@ -8883,7 +9064,10 @@
         <f t="shared" si="7"/>
         <v>132</v>
       </c>
-      <c r="AM69" s="1"/>
+      <c r="AM69" s="1">
+        <f t="shared" si="8"/>
+        <v>585.73479999999995</v>
+      </c>
       <c r="AN69" s="1"/>
       <c r="AO69" s="1"/>
       <c r="AP69" s="1"/>
@@ -8927,7 +9111,7 @@
         <v>205.9</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="19">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="20">E70-K70</f>
         <v>-18.954000000000008</v>
       </c>
       <c r="M70" s="1"/>
@@ -8948,11 +9132,11 @@
         <v>37.389200000000002</v>
       </c>
       <c r="W70" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>132.8934000000001</v>
       </c>
       <c r="X70" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>132.8934000000001</v>
       </c>
       <c r="Y70" s="1">
@@ -8998,7 +9182,10 @@
         <f t="shared" si="7"/>
         <v>133</v>
       </c>
-      <c r="AM70" s="1"/>
+      <c r="AM70" s="1">
+        <f t="shared" si="8"/>
+        <v>201.46012727272728</v>
+      </c>
       <c r="AN70" s="1"/>
       <c r="AO70" s="1"/>
       <c r="AP70" s="1"/>
@@ -9042,7 +9229,7 @@
         <v>12</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M71" s="1"/>
@@ -9059,20 +9246,20 @@
       <c r="T71" s="1"/>
       <c r="U71" s="1"/>
       <c r="V71" s="1">
-        <f t="shared" ref="V71:V132" si="20">E71/5</f>
+        <f t="shared" ref="V71:V132" si="21">E71/5</f>
         <v>2.4</v>
       </c>
       <c r="W71" s="5"/>
       <c r="X71" s="5">
-        <f t="shared" ref="X71:X132" si="21">W71</f>
+        <f t="shared" ref="X71:X132" si="22">W71</f>
         <v>0</v>
       </c>
       <c r="Y71" s="1">
-        <f t="shared" ref="Y71:Y132" si="22">(F71+O71+P71+Q71+R71+S71+T71+U71+X71)/V71</f>
+        <f t="shared" ref="Y71:Y132" si="23">(F71+O71+P71+Q71+R71+S71+T71+U71+X71)/V71</f>
         <v>26.708333333333332</v>
       </c>
       <c r="Z71" s="1">
-        <f t="shared" ref="Z71:Z132" si="23">(F71+O71+P71+Q71+R71+S71+T71+U71)/V71</f>
+        <f t="shared" ref="Z71:Z132" si="24">(F71+O71+P71+Q71+R71+S71+T71+U71)/V71</f>
         <v>26.708333333333332</v>
       </c>
       <c r="AA71" s="1">
@@ -9105,14 +9292,17 @@
       <c r="AJ71" s="1">
         <v>4.8</v>
       </c>
-      <c r="AK71" s="14" t="s">
+      <c r="AK71" s="13" t="s">
         <v>106</v>
       </c>
       <c r="AL71" s="1">
-        <f t="shared" ref="AL71:AL132" si="24">ROUND(G71*X71,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AM71" s="1"/>
+        <f t="shared" ref="AL71:AL132" si="25">ROUND(G71*X71,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AM71" s="1">
+        <f t="shared" ref="AM71:AM132" si="26">(SUM(AA71:AJ71)+V71)/11*7</f>
+        <v>21</v>
+      </c>
       <c r="AN71" s="1"/>
       <c r="AO71" s="1"/>
       <c r="AP71" s="1"/>
@@ -9156,7 +9346,7 @@
         <v>444.35</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-17.605000000000018</v>
       </c>
       <c r="M72" s="1"/>
@@ -9179,7 +9369,7 @@
         <v>-202.8</v>
       </c>
       <c r="V72" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>85.349000000000004</v>
       </c>
       <c r="W72" s="5">
@@ -9191,11 +9381,11 @@
         <v>518.57560000000001</v>
       </c>
       <c r="Y72" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="Z72" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2.9240576925330104</v>
       </c>
       <c r="AA72" s="1">
@@ -9230,10 +9420,13 @@
       </c>
       <c r="AK72" s="1"/>
       <c r="AL72" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>519</v>
       </c>
-      <c r="AM72" s="1"/>
+      <c r="AM72" s="1">
+        <f t="shared" si="26"/>
+        <v>399.59932727272729</v>
+      </c>
       <c r="AN72" s="1"/>
       <c r="AO72" s="1"/>
       <c r="AP72" s="1"/>
@@ -9265,7 +9458,7 @@
       <c r="J73" s="10"/>
       <c r="K73" s="10"/>
       <c r="L73" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M73" s="10"/>
@@ -9280,22 +9473,22 @@
       <c r="T73" s="10"/>
       <c r="U73" s="10"/>
       <c r="V73" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W73" s="12"/>
       <c r="X73" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y73" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z73" s="10" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="Z73" s="10" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AA73" s="10">
         <v>0</v>
       </c>
@@ -9330,10 +9523,13 @@
         <v>51</v>
       </c>
       <c r="AL73" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM73" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM73" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="AN73" s="1"/>
       <c r="AO73" s="1"/>
       <c r="AP73" s="1"/>
@@ -9375,7 +9571,7 @@
         <v>121</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-1</v>
       </c>
       <c r="M74" s="1"/>
@@ -9392,23 +9588,23 @@
       <c r="T74" s="1"/>
       <c r="U74" s="1"/>
       <c r="V74" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>24</v>
       </c>
       <c r="W74" s="5">
-        <f t="shared" ref="W74:W76" si="25">12*V74-U74-T74-S74-R74-Q74-P74-O74-F74</f>
+        <f t="shared" ref="W74:W76" si="27">12*V74-U74-T74-S74-R74-Q74-P74-O74-F74</f>
         <v>143</v>
       </c>
       <c r="X74" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>143</v>
       </c>
       <c r="Y74" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12</v>
       </c>
       <c r="Z74" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6.041666666666667</v>
       </c>
       <c r="AA74" s="1">
@@ -9443,10 +9639,13 @@
       </c>
       <c r="AK74" s="1"/>
       <c r="AL74" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>86</v>
       </c>
-      <c r="AM74" s="1"/>
+      <c r="AM74" s="1">
+        <f t="shared" si="26"/>
+        <v>93.545454545454547</v>
+      </c>
       <c r="AN74" s="1"/>
       <c r="AO74" s="1"/>
       <c r="AP74" s="1"/>
@@ -9490,7 +9689,7 @@
         <v>90</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2</v>
       </c>
       <c r="M75" s="1"/>
@@ -9507,23 +9706,23 @@
       <c r="T75" s="1"/>
       <c r="U75" s="1"/>
       <c r="V75" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>18.399999999999999</v>
       </c>
       <c r="W75" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>29.19999999999996</v>
       </c>
       <c r="X75" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>29.19999999999996</v>
       </c>
       <c r="Y75" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12</v>
       </c>
       <c r="Z75" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>10.413043478260871</v>
       </c>
       <c r="AA75" s="1">
@@ -9558,10 +9757,13 @@
       </c>
       <c r="AK75" s="1"/>
       <c r="AL75" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>12</v>
       </c>
-      <c r="AM75" s="1"/>
+      <c r="AM75" s="1">
+        <f t="shared" si="26"/>
+        <v>129.43636363636361</v>
+      </c>
       <c r="AN75" s="1"/>
       <c r="AO75" s="1"/>
       <c r="AP75" s="1"/>
@@ -9605,7 +9807,7 @@
         <v>117</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4</v>
       </c>
       <c r="M76" s="1"/>
@@ -9624,23 +9826,23 @@
       <c r="T76" s="1"/>
       <c r="U76" s="1"/>
       <c r="V76" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>24.2</v>
       </c>
       <c r="W76" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>86.799999999999955</v>
       </c>
       <c r="X76" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>86.799999999999955</v>
       </c>
       <c r="Y76" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12</v>
       </c>
       <c r="Z76" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>8.4132231404958695</v>
       </c>
       <c r="AA76" s="1">
@@ -9675,10 +9877,13 @@
       </c>
       <c r="AK76" s="1"/>
       <c r="AL76" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>29</v>
       </c>
-      <c r="AM76" s="1"/>
+      <c r="AM76" s="1">
+        <f t="shared" si="26"/>
+        <v>164.69090909090909</v>
+      </c>
       <c r="AN76" s="1"/>
       <c r="AO76" s="1"/>
       <c r="AP76" s="1"/>
@@ -9722,7 +9927,7 @@
         <v>61</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-5</v>
       </c>
       <c r="M77" s="1"/>
@@ -9739,22 +9944,22 @@
       <c r="T77" s="1"/>
       <c r="U77" s="1"/>
       <c r="V77" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>11.2</v>
       </c>
       <c r="W77" s="5"/>
       <c r="X77" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y77" s="1">
-        <f t="shared" si="22"/>
-        <v>13.214285714285715</v>
-      </c>
-      <c r="Z77" s="1">
         <f t="shared" si="23"/>
         <v>13.214285714285715</v>
       </c>
+      <c r="Z77" s="1">
+        <f t="shared" si="24"/>
+        <v>13.214285714285715</v>
+      </c>
       <c r="AA77" s="1">
         <v>13.4</v>
       </c>
@@ -9787,10 +9992,13 @@
       </c>
       <c r="AK77" s="1"/>
       <c r="AL77" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM77" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM77" s="1">
+        <f t="shared" si="26"/>
+        <v>99.018181818181816</v>
+      </c>
       <c r="AN77" s="1"/>
       <c r="AO77" s="1"/>
       <c r="AP77" s="1"/>
@@ -9834,7 +10042,7 @@
         <v>231</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-1</v>
       </c>
       <c r="M78" s="1"/>
@@ -9851,7 +10059,7 @@
       <c r="T78" s="1"/>
       <c r="U78" s="1"/>
       <c r="V78" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>46</v>
       </c>
       <c r="W78" s="5">
@@ -9863,11 +10071,11 @@
         <v>266</v>
       </c>
       <c r="Y78" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="Z78" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4.2173913043478262</v>
       </c>
       <c r="AA78" s="1">
@@ -9902,10 +10110,13 @@
       </c>
       <c r="AK78" s="1"/>
       <c r="AL78" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>98</v>
       </c>
-      <c r="AM78" s="1"/>
+      <c r="AM78" s="1">
+        <f t="shared" si="26"/>
+        <v>224.5090909090909</v>
+      </c>
       <c r="AN78" s="1"/>
       <c r="AO78" s="1"/>
       <c r="AP78" s="1"/>
@@ -9939,7 +10150,7 @@
         <v>6</v>
       </c>
       <c r="L79" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-6</v>
       </c>
       <c r="M79" s="10"/>
@@ -9954,22 +10165,22 @@
       <c r="T79" s="10"/>
       <c r="U79" s="10"/>
       <c r="V79" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W79" s="12"/>
       <c r="X79" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y79" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z79" s="10" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="Z79" s="10" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AA79" s="10">
         <v>0</v>
       </c>
@@ -10004,10 +10215,13 @@
         <v>51</v>
       </c>
       <c r="AL79" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM79" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM79" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="AN79" s="1"/>
       <c r="AO79" s="1"/>
       <c r="AP79" s="1"/>
@@ -10049,7 +10263,7 @@
         <v>50</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4</v>
       </c>
       <c r="M80" s="1"/>
@@ -10068,7 +10282,7 @@
       <c r="T80" s="1"/>
       <c r="U80" s="1"/>
       <c r="V80" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10.8</v>
       </c>
       <c r="W80" s="5">
@@ -10076,15 +10290,15 @@
         <v>74</v>
       </c>
       <c r="X80" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>74</v>
       </c>
       <c r="Y80" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>8.9999999999999982</v>
       </c>
       <c r="Z80" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2.1481481481481475</v>
       </c>
       <c r="AA80" s="1">
@@ -10119,10 +10333,13 @@
       </c>
       <c r="AK80" s="1"/>
       <c r="AL80" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>24</v>
       </c>
-      <c r="AM80" s="1"/>
+      <c r="AM80" s="1">
+        <f t="shared" si="26"/>
+        <v>52.690909090909088</v>
+      </c>
       <c r="AN80" s="1"/>
       <c r="AO80" s="1"/>
       <c r="AP80" s="1"/>
@@ -10164,7 +10381,7 @@
         <v>201</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>14</v>
       </c>
       <c r="M81" s="1"/>
@@ -10183,11 +10400,11 @@
       </c>
       <c r="U81" s="1"/>
       <c r="V81" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>43</v>
       </c>
       <c r="W81" s="5">
-        <f t="shared" ref="W81" si="26">12*V81-U81-T81-S81-R81-Q81-P81-O81-F81</f>
+        <f t="shared" ref="W81" si="28">12*V81-U81-T81-S81-R81-Q81-P81-O81-F81</f>
         <v>317.60000000000002</v>
       </c>
       <c r="X81" s="5">
@@ -10195,11 +10412,11 @@
         <v>274.60000000000002</v>
       </c>
       <c r="Y81" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="Z81" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4.6139534883720925</v>
       </c>
       <c r="AA81" s="1">
@@ -10234,10 +10451,13 @@
       </c>
       <c r="AK81" s="1"/>
       <c r="AL81" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>110</v>
       </c>
-      <c r="AM81" s="1"/>
+      <c r="AM81" s="1">
+        <f t="shared" si="26"/>
+        <v>123.7090909090909</v>
+      </c>
       <c r="AN81" s="1"/>
       <c r="AO81" s="1"/>
       <c r="AP81" s="1"/>
@@ -10279,7 +10499,7 @@
         <v>22</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-5</v>
       </c>
       <c r="M82" s="1"/>
@@ -10296,22 +10516,22 @@
       <c r="T82" s="1"/>
       <c r="U82" s="1"/>
       <c r="V82" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>3.4</v>
       </c>
       <c r="W82" s="5">
         <v>10</v>
       </c>
       <c r="X82" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>10</v>
       </c>
       <c r="Y82" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>20.882352941176471</v>
       </c>
       <c r="Z82" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>17.941176470588236</v>
       </c>
       <c r="AA82" s="1">
@@ -10346,10 +10566,13 @@
       </c>
       <c r="AK82" s="1"/>
       <c r="AL82" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>4</v>
       </c>
-      <c r="AM82" s="1"/>
+      <c r="AM82" s="1">
+        <f t="shared" si="26"/>
+        <v>39.836363636363636</v>
+      </c>
       <c r="AN82" s="1"/>
       <c r="AO82" s="1"/>
       <c r="AP82" s="1"/>
@@ -10393,7 +10616,7 @@
         <v>19</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-10</v>
       </c>
       <c r="M83" s="1"/>
@@ -10410,22 +10633,22 @@
       <c r="T83" s="1"/>
       <c r="U83" s="1"/>
       <c r="V83" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.8</v>
       </c>
       <c r="W83" s="5"/>
       <c r="X83" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y83" s="1">
-        <f t="shared" si="22"/>
-        <v>33.888888888888886</v>
-      </c>
-      <c r="Z83" s="1">
         <f t="shared" si="23"/>
         <v>33.888888888888886</v>
       </c>
+      <c r="Z83" s="1">
+        <f t="shared" si="24"/>
+        <v>33.888888888888886</v>
+      </c>
       <c r="AA83" s="1">
         <v>6.2</v>
       </c>
@@ -10456,14 +10679,17 @@
       <c r="AJ83" s="1">
         <v>4</v>
       </c>
-      <c r="AK83" s="14" t="s">
+      <c r="AK83" s="13" t="s">
         <v>106</v>
       </c>
       <c r="AL83" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM83" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM83" s="1">
+        <f t="shared" si="26"/>
+        <v>36.527272727272724</v>
+      </c>
       <c r="AN83" s="1"/>
       <c r="AO83" s="1"/>
       <c r="AP83" s="1"/>
@@ -10495,7 +10721,7 @@
       <c r="J84" s="10"/>
       <c r="K84" s="10"/>
       <c r="L84" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M84" s="10"/>
@@ -10510,22 +10736,22 @@
       <c r="T84" s="10"/>
       <c r="U84" s="10"/>
       <c r="V84" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W84" s="12"/>
       <c r="X84" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y84" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z84" s="10" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="Z84" s="10" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AA84" s="10">
         <v>0</v>
       </c>
@@ -10560,10 +10786,13 @@
         <v>51</v>
       </c>
       <c r="AL84" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM84" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM84" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="AN84" s="1"/>
       <c r="AO84" s="1"/>
       <c r="AP84" s="1"/>
@@ -10595,7 +10824,7 @@
       <c r="J85" s="10"/>
       <c r="K85" s="10"/>
       <c r="L85" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M85" s="10"/>
@@ -10610,22 +10839,22 @@
       <c r="T85" s="10"/>
       <c r="U85" s="10"/>
       <c r="V85" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W85" s="12"/>
       <c r="X85" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y85" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z85" s="10" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="Z85" s="10" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AA85" s="10">
         <v>0</v>
       </c>
@@ -10660,10 +10889,13 @@
         <v>51</v>
       </c>
       <c r="AL85" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM85" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM85" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="AN85" s="1"/>
       <c r="AO85" s="1"/>
       <c r="AP85" s="1"/>
@@ -10707,7 +10939,7 @@
         <v>138</v>
       </c>
       <c r="L86" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-1</v>
       </c>
       <c r="M86" s="10"/>
@@ -10724,22 +10956,22 @@
       <c r="T86" s="10"/>
       <c r="U86" s="10"/>
       <c r="V86" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>27.4</v>
       </c>
       <c r="W86" s="12"/>
       <c r="X86" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y86" s="1">
-        <f t="shared" si="22"/>
-        <v>1.3868613138686132</v>
-      </c>
-      <c r="Z86" s="10">
         <f t="shared" si="23"/>
         <v>1.3868613138686132</v>
       </c>
+      <c r="Z86" s="10">
+        <f t="shared" si="24"/>
+        <v>1.3868613138686132</v>
+      </c>
       <c r="AA86" s="10">
         <v>18.600000000000001</v>
       </c>
@@ -10772,10 +11004,13 @@
       </c>
       <c r="AK86" s="10"/>
       <c r="AL86" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM86" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM86" s="1">
+        <f t="shared" si="26"/>
+        <v>99.272727272727266</v>
+      </c>
       <c r="AN86" s="1"/>
       <c r="AO86" s="1"/>
       <c r="AP86" s="1"/>
@@ -10817,7 +11052,7 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="L87" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.8190000000000008</v>
       </c>
       <c r="M87" s="1"/>
@@ -10834,22 +11069,22 @@
       <c r="T87" s="1"/>
       <c r="U87" s="1"/>
       <c r="V87" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.3037999999999998</v>
       </c>
       <c r="W87" s="5"/>
       <c r="X87" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y87" s="1">
-        <f t="shared" si="22"/>
-        <v>10.562982897820993</v>
-      </c>
-      <c r="Z87" s="1">
         <f t="shared" si="23"/>
         <v>10.562982897820993</v>
       </c>
+      <c r="Z87" s="1">
+        <f t="shared" si="24"/>
+        <v>10.562982897820993</v>
+      </c>
       <c r="AA87" s="1">
         <v>0.86639999999999995</v>
       </c>
@@ -10882,10 +11117,13 @@
       </c>
       <c r="AK87" s="1"/>
       <c r="AL87" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM87" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM87" s="1">
+        <f t="shared" si="26"/>
+        <v>10.30730909090909</v>
+      </c>
       <c r="AN87" s="1"/>
       <c r="AO87" s="1"/>
       <c r="AP87" s="1"/>
@@ -10929,7 +11167,7 @@
         <v>326.94</v>
       </c>
       <c r="L88" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.0199999999999818</v>
       </c>
       <c r="M88" s="1"/>
@@ -10946,11 +11184,11 @@
       <c r="T88" s="1"/>
       <c r="U88" s="1"/>
       <c r="V88" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>65.792000000000002</v>
       </c>
       <c r="W88" s="5">
-        <f t="shared" ref="W88" si="27">12*V88-U88-T88-S88-R88-Q88-P88-O88-F88</f>
+        <f t="shared" ref="W88" si="29">12*V88-U88-T88-S88-R88-Q88-P88-O88-F88</f>
         <v>347.04429200000004</v>
       </c>
       <c r="X88" s="5">
@@ -10958,11 +11196,11 @@
         <v>281.25229200000001</v>
       </c>
       <c r="Y88" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="Z88" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6.7251293166342405</v>
       </c>
       <c r="AA88" s="1">
@@ -10997,10 +11235,13 @@
       </c>
       <c r="AK88" s="1"/>
       <c r="AL88" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>281</v>
       </c>
-      <c r="AM88" s="1"/>
+      <c r="AM88" s="1">
+        <f t="shared" si="26"/>
+        <v>384.42727272727274</v>
+      </c>
       <c r="AN88" s="1"/>
       <c r="AO88" s="1"/>
       <c r="AP88" s="1"/>
@@ -11032,7 +11273,7 @@
       <c r="J89" s="10"/>
       <c r="K89" s="10"/>
       <c r="L89" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M89" s="10"/>
@@ -11047,22 +11288,22 @@
       <c r="T89" s="10"/>
       <c r="U89" s="10"/>
       <c r="V89" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W89" s="12"/>
       <c r="X89" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y89" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z89" s="10" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="Z89" s="10" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AA89" s="10">
         <v>0</v>
       </c>
@@ -11097,10 +11338,13 @@
         <v>51</v>
       </c>
       <c r="AL89" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM89" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM89" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="AN89" s="1"/>
       <c r="AO89" s="1"/>
       <c r="AP89" s="1"/>
@@ -11144,7 +11388,7 @@
         <v>1654.5</v>
       </c>
       <c r="L90" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-2.9919999999999618</v>
       </c>
       <c r="M90" s="1"/>
@@ -11163,23 +11407,23 @@
       </c>
       <c r="U90" s="1"/>
       <c r="V90" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>330.30160000000001</v>
       </c>
       <c r="W90" s="5">
-        <f t="shared" ref="W90:W91" si="28">12*V90-U90-T90-S90-R90-Q90-P90-O90-F90</f>
+        <f t="shared" ref="W90:W91" si="30">12*V90-U90-T90-S90-R90-Q90-P90-O90-F90</f>
         <v>800.94381808000162</v>
       </c>
       <c r="X90" s="5">
-        <f t="shared" ref="X90" si="29">W90+$X$1*V90</f>
+        <f t="shared" ref="X90" si="31">W90+$X$1*V90</f>
         <v>470.64221808000161</v>
       </c>
       <c r="Y90" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
       <c r="Z90" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9.5751137200667458</v>
       </c>
       <c r="AA90" s="1">
@@ -11214,10 +11458,13 @@
       </c>
       <c r="AK90" s="1"/>
       <c r="AL90" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>471</v>
       </c>
-      <c r="AM90" s="1"/>
+      <c r="AM90" s="1">
+        <f t="shared" si="26"/>
+        <v>2237.8129454545451</v>
+      </c>
       <c r="AN90" s="1"/>
       <c r="AO90" s="1"/>
       <c r="AP90" s="1"/>
@@ -11261,7 +11508,7 @@
         <v>1682.5</v>
       </c>
       <c r="L91" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-13.305000000000064</v>
       </c>
       <c r="M91" s="1"/>
@@ -11284,24 +11531,24 @@
       </c>
       <c r="U91" s="1"/>
       <c r="V91" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>333.839</v>
       </c>
       <c r="W91" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>316.49047535999989</v>
       </c>
       <c r="X91" s="5">
         <v>0</v>
       </c>
       <c r="Y91" s="1">
-        <f t="shared" si="22"/>
-        <v>11.051966740374853</v>
-      </c>
-      <c r="Z91" s="1">
         <f t="shared" si="23"/>
         <v>11.051966740374853</v>
       </c>
+      <c r="Z91" s="1">
+        <f t="shared" si="24"/>
+        <v>11.051966740374853</v>
+      </c>
       <c r="AA91" s="1">
         <v>299.80560000000003</v>
       </c>
@@ -11334,10 +11581,13 @@
       </c>
       <c r="AK91" s="1"/>
       <c r="AL91" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM91" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM91" s="1">
+        <f t="shared" si="26"/>
+        <v>2332.2915636363632</v>
+      </c>
       <c r="AN91" s="1"/>
       <c r="AO91" s="1"/>
       <c r="AP91" s="1"/>
@@ -11381,7 +11631,7 @@
         <v>2655.0239999999999</v>
       </c>
       <c r="L92" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-13.222999999999956</v>
       </c>
       <c r="M92" s="1"/>
@@ -11404,22 +11654,22 @@
       </c>
       <c r="U92" s="1"/>
       <c r="V92" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>528.36019999999996</v>
       </c>
       <c r="W92" s="5"/>
       <c r="X92" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y92" s="1">
-        <f t="shared" si="22"/>
-        <v>12.568524949305418</v>
-      </c>
-      <c r="Z92" s="1">
         <f t="shared" si="23"/>
         <v>12.568524949305418</v>
       </c>
+      <c r="Z92" s="1">
+        <f t="shared" si="24"/>
+        <v>12.568524949305418</v>
+      </c>
       <c r="AA92" s="1">
         <v>520.89139999999998</v>
       </c>
@@ -11452,10 +11702,13 @@
       </c>
       <c r="AK92" s="1"/>
       <c r="AL92" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM92" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM92" s="1">
+        <f t="shared" si="26"/>
+        <v>3868.8577454545452</v>
+      </c>
       <c r="AN92" s="1"/>
       <c r="AO92" s="1"/>
       <c r="AP92" s="1"/>
@@ -11487,7 +11740,7 @@
       <c r="J93" s="10"/>
       <c r="K93" s="10"/>
       <c r="L93" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M93" s="10"/>
@@ -11502,22 +11755,22 @@
       <c r="T93" s="10"/>
       <c r="U93" s="10"/>
       <c r="V93" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W93" s="12"/>
       <c r="X93" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y93" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z93" s="10" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="Z93" s="10" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AA93" s="10">
         <v>0</v>
       </c>
@@ -11552,10 +11805,13 @@
         <v>51</v>
       </c>
       <c r="AL93" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM93" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM93" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="AN93" s="1"/>
       <c r="AO93" s="1"/>
       <c r="AP93" s="1"/>
@@ -11599,7 +11855,7 @@
         <v>169</v>
       </c>
       <c r="L94" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-25</v>
       </c>
       <c r="M94" s="1"/>
@@ -11616,7 +11872,7 @@
       <c r="T94" s="1"/>
       <c r="U94" s="1"/>
       <c r="V94" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>28.8</v>
       </c>
       <c r="W94" s="5">
@@ -11624,15 +11880,15 @@
         <v>212</v>
       </c>
       <c r="X94" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>212</v>
       </c>
       <c r="Y94" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="Z94" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2.6388888888888888</v>
       </c>
       <c r="AA94" s="1">
@@ -11667,10 +11923,13 @@
       </c>
       <c r="AK94" s="1"/>
       <c r="AL94" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>64</v>
       </c>
-      <c r="AM94" s="1"/>
+      <c r="AM94" s="1">
+        <f t="shared" si="26"/>
+        <v>148.90909090909093</v>
+      </c>
       <c r="AN94" s="1"/>
       <c r="AO94" s="1"/>
       <c r="AP94" s="1"/>
@@ -11702,7 +11961,7 @@
       <c r="J95" s="10"/>
       <c r="K95" s="10"/>
       <c r="L95" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M95" s="10"/>
@@ -11717,22 +11976,22 @@
       <c r="T95" s="10"/>
       <c r="U95" s="10"/>
       <c r="V95" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W95" s="12"/>
       <c r="X95" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y95" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z95" s="10" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="Z95" s="10" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AA95" s="10">
         <v>0</v>
       </c>
@@ -11767,10 +12026,13 @@
         <v>51</v>
       </c>
       <c r="AL95" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM95" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM95" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="AN95" s="1"/>
       <c r="AO95" s="1"/>
       <c r="AP95" s="1"/>
@@ -11814,7 +12076,7 @@
         <v>64</v>
       </c>
       <c r="L96" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-4</v>
       </c>
       <c r="M96" s="1"/>
@@ -11831,22 +12093,22 @@
       <c r="T96" s="1"/>
       <c r="U96" s="1"/>
       <c r="V96" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
       <c r="W96" s="5"/>
       <c r="X96" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y96" s="1">
-        <f t="shared" si="22"/>
-        <v>17.541666666666668</v>
-      </c>
-      <c r="Z96" s="1">
         <f t="shared" si="23"/>
         <v>17.541666666666668</v>
       </c>
+      <c r="Z96" s="1">
+        <f t="shared" si="24"/>
+        <v>17.541666666666668</v>
+      </c>
       <c r="AA96" s="1">
         <v>13</v>
       </c>
@@ -11881,10 +12143,13 @@
         <v>139</v>
       </c>
       <c r="AL96" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM96" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM96" s="1">
+        <f t="shared" si="26"/>
+        <v>77.381818181818176</v>
+      </c>
       <c r="AN96" s="1"/>
       <c r="AO96" s="1"/>
       <c r="AP96" s="1"/>
@@ -11924,7 +12189,7 @@
         <v>1</v>
       </c>
       <c r="L97" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-1</v>
       </c>
       <c r="M97" s="1"/>
@@ -11941,22 +12206,22 @@
       <c r="T97" s="1"/>
       <c r="U97" s="1"/>
       <c r="V97" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W97" s="5"/>
       <c r="X97" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y97" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z97" s="1" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="Z97" s="1" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AA97" s="1">
         <v>0</v>
       </c>
@@ -11989,10 +12254,13 @@
       </c>
       <c r="AK97" s="1"/>
       <c r="AL97" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM97" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM97" s="1">
+        <f t="shared" si="26"/>
+        <v>35</v>
+      </c>
       <c r="AN97" s="1"/>
       <c r="AO97" s="1"/>
       <c r="AP97" s="1"/>
@@ -12034,7 +12302,7 @@
         <v>73</v>
       </c>
       <c r="L98" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4</v>
       </c>
       <c r="M98" s="1"/>
@@ -12051,23 +12319,23 @@
       <c r="T98" s="1"/>
       <c r="U98" s="1"/>
       <c r="V98" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>15.4</v>
       </c>
       <c r="W98" s="5">
-        <f t="shared" ref="W98" si="30">12*V98-U98-T98-S98-R98-Q98-P98-O98-F98</f>
+        <f t="shared" ref="W98" si="32">12*V98-U98-T98-S98-R98-Q98-P98-O98-F98</f>
         <v>44.600000000000023</v>
       </c>
       <c r="X98" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>44.600000000000023</v>
       </c>
       <c r="Y98" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12</v>
       </c>
       <c r="Z98" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9.103896103896103</v>
       </c>
       <c r="AA98" s="1">
@@ -12102,10 +12370,13 @@
       </c>
       <c r="AK98" s="1"/>
       <c r="AL98" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>3</v>
       </c>
-      <c r="AM98" s="1"/>
+      <c r="AM98" s="1">
+        <f t="shared" si="26"/>
+        <v>62.236363636363635</v>
+      </c>
       <c r="AN98" s="1"/>
       <c r="AO98" s="1"/>
       <c r="AP98" s="1"/>
@@ -12147,7 +12418,7 @@
         <v>70</v>
       </c>
       <c r="L99" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>5</v>
       </c>
       <c r="M99" s="10"/>
@@ -12164,22 +12435,22 @@
       <c r="T99" s="10"/>
       <c r="U99" s="10"/>
       <c r="V99" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>15</v>
       </c>
       <c r="W99" s="12"/>
       <c r="X99" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y99" s="1">
-        <f t="shared" si="22"/>
-        <v>7.666666666666667</v>
-      </c>
-      <c r="Z99" s="10">
         <f t="shared" si="23"/>
         <v>7.666666666666667</v>
       </c>
+      <c r="Z99" s="10">
+        <f t="shared" si="24"/>
+        <v>7.666666666666667</v>
+      </c>
       <c r="AA99" s="10">
         <v>12.6</v>
       </c>
@@ -12212,10 +12483,13 @@
       </c>
       <c r="AK99" s="10"/>
       <c r="AL99" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM99" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM99" s="1">
+        <f t="shared" si="26"/>
+        <v>75.090909090909093</v>
+      </c>
       <c r="AN99" s="1"/>
       <c r="AO99" s="1"/>
       <c r="AP99" s="1"/>
@@ -12255,7 +12529,7 @@
         <v>41</v>
       </c>
       <c r="L100" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-42</v>
       </c>
       <c r="M100" s="10"/>
@@ -12272,22 +12546,22 @@
       <c r="T100" s="10"/>
       <c r="U100" s="10"/>
       <c r="V100" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-0.2</v>
       </c>
       <c r="W100" s="12"/>
       <c r="X100" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y100" s="1">
-        <f t="shared" si="22"/>
-        <v>-5</v>
-      </c>
-      <c r="Z100" s="10">
         <f t="shared" si="23"/>
         <v>-5</v>
       </c>
+      <c r="Z100" s="10">
+        <f t="shared" si="24"/>
+        <v>-5</v>
+      </c>
       <c r="AA100" s="10">
         <v>-0.8</v>
       </c>
@@ -12322,10 +12596,13 @@
         <v>144</v>
       </c>
       <c r="AL100" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM100" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM100" s="1">
+        <f t="shared" si="26"/>
+        <v>44.927272727272722</v>
+      </c>
       <c r="AN100" s="1"/>
       <c r="AO100" s="1"/>
       <c r="AP100" s="1"/>
@@ -12357,7 +12634,7 @@
       <c r="J101" s="10"/>
       <c r="K101" s="10"/>
       <c r="L101" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M101" s="10"/>
@@ -12372,22 +12649,22 @@
       <c r="T101" s="10"/>
       <c r="U101" s="10"/>
       <c r="V101" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W101" s="12"/>
       <c r="X101" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y101" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z101" s="10" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="Z101" s="10" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AA101" s="10">
         <v>0</v>
       </c>
@@ -12422,10 +12699,13 @@
         <v>51</v>
       </c>
       <c r="AL101" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM101" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM101" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="AN101" s="1"/>
       <c r="AO101" s="1"/>
       <c r="AP101" s="1"/>
@@ -12465,7 +12745,7 @@
         <v>31</v>
       </c>
       <c r="L102" s="10">
-        <f t="shared" ref="L102:L132" si="31">E102-K102</f>
+        <f t="shared" ref="L102:L132" si="33">E102-K102</f>
         <v>1.0480000000000018</v>
       </c>
       <c r="M102" s="10"/>
@@ -12482,22 +12762,22 @@
       <c r="T102" s="10"/>
       <c r="U102" s="10"/>
       <c r="V102" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6.4096000000000002</v>
       </c>
       <c r="W102" s="12"/>
       <c r="X102" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y102" s="1">
-        <f t="shared" si="22"/>
-        <v>-0.24619321018472293</v>
-      </c>
-      <c r="Z102" s="10">
         <f t="shared" si="23"/>
         <v>-0.24619321018472293</v>
       </c>
+      <c r="Z102" s="10">
+        <f t="shared" si="24"/>
+        <v>-0.24619321018472293</v>
+      </c>
       <c r="AA102" s="10">
         <v>3.5326</v>
       </c>
@@ -12532,10 +12812,13 @@
         <v>51</v>
       </c>
       <c r="AL102" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM102" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM102" s="1">
+        <f t="shared" si="26"/>
+        <v>37.45483636363636</v>
+      </c>
       <c r="AN102" s="1"/>
       <c r="AO102" s="1"/>
       <c r="AP102" s="1"/>
@@ -12567,7 +12850,7 @@
       <c r="J103" s="10"/>
       <c r="K103" s="10"/>
       <c r="L103" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M103" s="10"/>
@@ -12582,22 +12865,22 @@
       <c r="T103" s="10"/>
       <c r="U103" s="10"/>
       <c r="V103" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W103" s="12"/>
       <c r="X103" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y103" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z103" s="10" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="Z103" s="10" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AA103" s="10">
         <v>0</v>
       </c>
@@ -12632,10 +12915,13 @@
         <v>51</v>
       </c>
       <c r="AL103" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM103" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM103" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="AN103" s="1"/>
       <c r="AO103" s="1"/>
       <c r="AP103" s="1"/>
@@ -12667,7 +12953,7 @@
       <c r="J104" s="10"/>
       <c r="K104" s="10"/>
       <c r="L104" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M104" s="10"/>
@@ -12682,22 +12968,22 @@
       <c r="T104" s="10"/>
       <c r="U104" s="10"/>
       <c r="V104" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W104" s="12"/>
       <c r="X104" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y104" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z104" s="10" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="Z104" s="10" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AA104" s="10">
         <v>0</v>
       </c>
@@ -12732,10 +13018,13 @@
         <v>51</v>
       </c>
       <c r="AL104" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM104" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM104" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="AN104" s="1"/>
       <c r="AO104" s="1"/>
       <c r="AP104" s="1"/>
@@ -12779,7 +13068,7 @@
         <v>58</v>
       </c>
       <c r="L105" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-8</v>
       </c>
       <c r="M105" s="1"/>
@@ -12796,22 +13085,22 @@
       <c r="T105" s="1"/>
       <c r="U105" s="1"/>
       <c r="V105" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10</v>
       </c>
       <c r="W105" s="5"/>
       <c r="X105" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y105" s="1">
-        <f t="shared" si="22"/>
-        <v>20.52</v>
-      </c>
-      <c r="Z105" s="1">
         <f t="shared" si="23"/>
         <v>20.52</v>
       </c>
+      <c r="Z105" s="1">
+        <f t="shared" si="24"/>
+        <v>20.52</v>
+      </c>
       <c r="AA105" s="1">
         <v>18.399999999999999</v>
       </c>
@@ -12844,10 +13133,13 @@
       </c>
       <c r="AK105" s="1"/>
       <c r="AL105" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM105" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM105" s="1">
+        <f t="shared" si="26"/>
+        <v>81.581818181818178</v>
+      </c>
       <c r="AN105" s="1"/>
       <c r="AO105" s="1"/>
       <c r="AP105" s="1"/>
@@ -12891,7 +13183,7 @@
         <v>71</v>
       </c>
       <c r="L106" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-24</v>
       </c>
       <c r="M106" s="1"/>
@@ -12908,22 +13200,22 @@
       <c r="T106" s="1"/>
       <c r="U106" s="1"/>
       <c r="V106" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>9.4</v>
       </c>
       <c r="W106" s="5"/>
       <c r="X106" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y106" s="1">
-        <f t="shared" si="22"/>
-        <v>22.393617021276594</v>
-      </c>
-      <c r="Z106" s="1">
         <f t="shared" si="23"/>
         <v>22.393617021276594</v>
       </c>
+      <c r="Z106" s="1">
+        <f t="shared" si="24"/>
+        <v>22.393617021276594</v>
+      </c>
       <c r="AA106" s="1">
         <v>16.8</v>
       </c>
@@ -12958,10 +13250,13 @@
         <v>151</v>
       </c>
       <c r="AL106" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM106" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM106" s="1">
+        <f t="shared" si="26"/>
+        <v>116.32727272727274</v>
+      </c>
       <c r="AN106" s="1"/>
       <c r="AO106" s="1"/>
       <c r="AP106" s="1"/>
@@ -12993,7 +13288,7 @@
       <c r="J107" s="10"/>
       <c r="K107" s="10"/>
       <c r="L107" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M107" s="10"/>
@@ -13008,22 +13303,22 @@
       <c r="T107" s="10"/>
       <c r="U107" s="10"/>
       <c r="V107" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W107" s="12"/>
       <c r="X107" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y107" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z107" s="10" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="Z107" s="10" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AA107" s="10">
         <v>0</v>
       </c>
@@ -13058,10 +13353,13 @@
         <v>51</v>
       </c>
       <c r="AL107" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM107" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM107" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="AN107" s="1"/>
       <c r="AO107" s="1"/>
       <c r="AP107" s="1"/>
@@ -13105,7 +13403,7 @@
         <v>195.9</v>
       </c>
       <c r="L108" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.12699999999998113</v>
       </c>
       <c r="M108" s="1"/>
@@ -13122,23 +13420,23 @@
       <c r="T108" s="1"/>
       <c r="U108" s="1"/>
       <c r="V108" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>39.205399999999997</v>
       </c>
       <c r="W108" s="5">
-        <f t="shared" ref="W108:W110" si="32">12*V108-U108-T108-S108-R108-Q108-P108-O108-F108</f>
+        <f t="shared" ref="W108:W110" si="34">12*V108-U108-T108-S108-R108-Q108-P108-O108-F108</f>
         <v>31.994600000000077</v>
       </c>
       <c r="X108" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>31.994600000000077</v>
       </c>
       <c r="Y108" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12</v>
       </c>
       <c r="Z108" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>11.183923643171601</v>
       </c>
       <c r="AA108" s="1">
@@ -13173,10 +13471,13 @@
       </c>
       <c r="AK108" s="1"/>
       <c r="AL108" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>32</v>
       </c>
-      <c r="AM108" s="1"/>
+      <c r="AM108" s="1">
+        <f t="shared" si="26"/>
+        <v>298.83623636363643</v>
+      </c>
       <c r="AN108" s="1"/>
       <c r="AO108" s="1"/>
       <c r="AP108" s="1"/>
@@ -13220,7 +13521,7 @@
         <v>219.03</v>
       </c>
       <c r="L109" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-3.1239999999999952</v>
       </c>
       <c r="M109" s="1"/>
@@ -13237,23 +13538,23 @@
       <c r="T109" s="1"/>
       <c r="U109" s="1"/>
       <c r="V109" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>43.181200000000004</v>
       </c>
       <c r="W109" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>112.81614447999999</v>
       </c>
       <c r="X109" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>112.81614447999999</v>
       </c>
       <c r="Y109" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12.000000000000002</v>
       </c>
       <c r="Z109" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9.3873781997721242</v>
       </c>
       <c r="AA109" s="1">
@@ -13288,10 +13589,13 @@
       </c>
       <c r="AK109" s="1"/>
       <c r="AL109" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>113</v>
       </c>
-      <c r="AM109" s="1"/>
+      <c r="AM109" s="1">
+        <f t="shared" si="26"/>
+        <v>353.41447272727271</v>
+      </c>
       <c r="AN109" s="1"/>
       <c r="AO109" s="1"/>
       <c r="AP109" s="1"/>
@@ -13335,7 +13639,7 @@
         <v>286.52</v>
       </c>
       <c r="L110" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-1.4559999999999604</v>
       </c>
       <c r="M110" s="1"/>
@@ -13354,23 +13658,23 @@
       </c>
       <c r="U110" s="1"/>
       <c r="V110" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>57.012800000000006</v>
       </c>
       <c r="W110" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>71.740920000000187</v>
       </c>
       <c r="X110" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>71.740920000000187</v>
       </c>
       <c r="Y110" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12</v>
       </c>
       <c r="Z110" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>10.741669940785224</v>
       </c>
       <c r="AA110" s="1">
@@ -13405,10 +13709,13 @@
       </c>
       <c r="AK110" s="1"/>
       <c r="AL110" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>72</v>
       </c>
-      <c r="AM110" s="1"/>
+      <c r="AM110" s="1">
+        <f t="shared" si="26"/>
+        <v>397.27316363636362</v>
+      </c>
       <c r="AN110" s="1"/>
       <c r="AO110" s="1"/>
       <c r="AP110" s="1"/>
@@ -13440,7 +13747,7 @@
       <c r="J111" s="10"/>
       <c r="K111" s="10"/>
       <c r="L111" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M111" s="10"/>
@@ -13455,22 +13762,22 @@
       <c r="T111" s="10"/>
       <c r="U111" s="10"/>
       <c r="V111" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W111" s="12"/>
       <c r="X111" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y111" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z111" s="10" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="Z111" s="10" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AA111" s="10">
         <v>0</v>
       </c>
@@ -13505,10 +13812,13 @@
         <v>51</v>
       </c>
       <c r="AL111" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM111" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM111" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="AN111" s="1"/>
       <c r="AO111" s="1"/>
       <c r="AP111" s="1"/>
@@ -13540,7 +13850,7 @@
       <c r="J112" s="10"/>
       <c r="K112" s="10"/>
       <c r="L112" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M112" s="10"/>
@@ -13555,22 +13865,22 @@
       <c r="T112" s="10"/>
       <c r="U112" s="10"/>
       <c r="V112" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W112" s="12"/>
       <c r="X112" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y112" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z112" s="10" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="Z112" s="10" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AA112" s="10">
         <v>0</v>
       </c>
@@ -13605,10 +13915,13 @@
         <v>51</v>
       </c>
       <c r="AL112" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM112" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM112" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="AN112" s="1"/>
       <c r="AO112" s="1"/>
       <c r="AP112" s="1"/>
@@ -13652,7 +13965,7 @@
         <v>169</v>
       </c>
       <c r="L113" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-160</v>
       </c>
       <c r="M113" s="1"/>
@@ -13669,22 +13982,22 @@
       <c r="T113" s="1"/>
       <c r="U113" s="1"/>
       <c r="V113" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.8</v>
       </c>
       <c r="W113" s="5"/>
       <c r="X113" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y113" s="1">
-        <f t="shared" si="22"/>
-        <v>241.72222222222223</v>
-      </c>
-      <c r="Z113" s="1">
         <f t="shared" si="23"/>
         <v>241.72222222222223</v>
       </c>
+      <c r="Z113" s="1">
+        <f t="shared" si="24"/>
+        <v>241.72222222222223</v>
+      </c>
       <c r="AA113" s="1">
         <v>20</v>
       </c>
@@ -13717,10 +14030,13 @@
       </c>
       <c r="AK113" s="1"/>
       <c r="AL113" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM113" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM113" s="1">
+        <f t="shared" si="26"/>
+        <v>129.56363636363639</v>
+      </c>
       <c r="AN113" s="1"/>
       <c r="AO113" s="1"/>
       <c r="AP113" s="1"/>
@@ -13764,7 +14080,7 @@
         <v>197</v>
       </c>
       <c r="L114" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>5</v>
       </c>
       <c r="M114" s="1"/>
@@ -13783,23 +14099,23 @@
       </c>
       <c r="U114" s="1"/>
       <c r="V114" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>40.4</v>
       </c>
       <c r="W114" s="5">
-        <f t="shared" ref="W114:W115" si="33">12*V114-U114-T114-S114-R114-Q114-P114-O114-F114</f>
+        <f t="shared" ref="W114:W115" si="35">12*V114-U114-T114-S114-R114-Q114-P114-O114-F114</f>
         <v>151.19999999999993</v>
       </c>
       <c r="X114" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>151.19999999999993</v>
       </c>
       <c r="Y114" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12</v>
       </c>
       <c r="Z114" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>8.2574257425742577</v>
       </c>
       <c r="AA114" s="1">
@@ -13834,10 +14150,13 @@
       </c>
       <c r="AK114" s="1"/>
       <c r="AL114" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>42</v>
       </c>
-      <c r="AM114" s="1"/>
+      <c r="AM114" s="1">
+        <f t="shared" si="26"/>
+        <v>143.18181818181819</v>
+      </c>
       <c r="AN114" s="1"/>
       <c r="AO114" s="1"/>
       <c r="AP114" s="1"/>
@@ -13881,7 +14200,7 @@
         <v>195</v>
       </c>
       <c r="L115" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M115" s="1"/>
@@ -13898,23 +14217,23 @@
       <c r="T115" s="1"/>
       <c r="U115" s="1"/>
       <c r="V115" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>39</v>
       </c>
       <c r="W115" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>108.39999999999998</v>
       </c>
       <c r="X115" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>108.39999999999998</v>
       </c>
       <c r="Y115" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12</v>
       </c>
       <c r="Z115" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9.2205128205128215</v>
       </c>
       <c r="AA115" s="1">
@@ -13949,10 +14268,13 @@
       </c>
       <c r="AK115" s="1"/>
       <c r="AL115" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>30</v>
       </c>
-      <c r="AM115" s="1"/>
+      <c r="AM115" s="1">
+        <f t="shared" si="26"/>
+        <v>250.85454545454544</v>
+      </c>
       <c r="AN115" s="1"/>
       <c r="AO115" s="1"/>
       <c r="AP115" s="1"/>
@@ -13984,7 +14306,7 @@
       <c r="J116" s="10"/>
       <c r="K116" s="10"/>
       <c r="L116" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M116" s="10"/>
@@ -13999,22 +14321,22 @@
       <c r="T116" s="10"/>
       <c r="U116" s="10"/>
       <c r="V116" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W116" s="12"/>
       <c r="X116" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y116" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z116" s="10" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="Z116" s="10" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AA116" s="10">
         <v>0</v>
       </c>
@@ -14049,10 +14371,13 @@
         <v>51</v>
       </c>
       <c r="AL116" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM116" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM116" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="AN116" s="1"/>
       <c r="AO116" s="1"/>
       <c r="AP116" s="1"/>
@@ -14094,7 +14419,7 @@
         <v>105</v>
       </c>
       <c r="L117" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-3.6869999999999976</v>
       </c>
       <c r="M117" s="1"/>
@@ -14111,23 +14436,23 @@
       <c r="T117" s="1"/>
       <c r="U117" s="1"/>
       <c r="V117" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>20.262599999999999</v>
       </c>
       <c r="W117" s="5">
-        <f t="shared" ref="W117:W118" si="34">12*V117-U117-T117-S117-R117-Q117-P117-O117-F117</f>
+        <f t="shared" ref="W117:W118" si="36">12*V117-U117-T117-S117-R117-Q117-P117-O117-F117</f>
         <v>91.156400000000019</v>
       </c>
       <c r="X117" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>91.156400000000019</v>
       </c>
       <c r="Y117" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12</v>
       </c>
       <c r="Z117" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>7.5012486058057695</v>
       </c>
       <c r="AA117" s="1">
@@ -14162,10 +14487,13 @@
       </c>
       <c r="AK117" s="1"/>
       <c r="AL117" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>91</v>
       </c>
-      <c r="AM117" s="1"/>
+      <c r="AM117" s="1">
+        <f t="shared" si="26"/>
+        <v>112.59118181818181</v>
+      </c>
       <c r="AN117" s="1"/>
       <c r="AO117" s="1"/>
       <c r="AP117" s="1"/>
@@ -14209,7 +14537,7 @@
         <v>82.5</v>
       </c>
       <c r="L118" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-2.5999999999996248E-2</v>
       </c>
       <c r="M118" s="1"/>
@@ -14226,23 +14554,23 @@
       <c r="T118" s="1"/>
       <c r="U118" s="1"/>
       <c r="V118" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>16.494800000000001</v>
       </c>
       <c r="W118" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>36.249400000000009</v>
       </c>
       <c r="X118" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>36.249400000000009</v>
       </c>
       <c r="Y118" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12</v>
       </c>
       <c r="Z118" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9.8023740815287255</v>
       </c>
       <c r="AA118" s="1">
@@ -14277,10 +14605,13 @@
       </c>
       <c r="AK118" s="1"/>
       <c r="AL118" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>36</v>
       </c>
-      <c r="AM118" s="1"/>
+      <c r="AM118" s="1">
+        <f t="shared" si="26"/>
+        <v>95.429218181818172</v>
+      </c>
       <c r="AN118" s="1"/>
       <c r="AO118" s="1"/>
       <c r="AP118" s="1"/>
@@ -14312,7 +14643,7 @@
       <c r="J119" s="10"/>
       <c r="K119" s="10"/>
       <c r="L119" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M119" s="10"/>
@@ -14327,22 +14658,22 @@
       <c r="T119" s="10"/>
       <c r="U119" s="10"/>
       <c r="V119" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W119" s="12"/>
       <c r="X119" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y119" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z119" s="10" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="Z119" s="10" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AA119" s="10">
         <v>0</v>
       </c>
@@ -14377,10 +14708,13 @@
         <v>51</v>
       </c>
       <c r="AL119" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM119" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM119" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="AN119" s="1"/>
       <c r="AO119" s="1"/>
       <c r="AP119" s="1"/>
@@ -14412,7 +14746,7 @@
       <c r="J120" s="10"/>
       <c r="K120" s="10"/>
       <c r="L120" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M120" s="10"/>
@@ -14427,22 +14761,22 @@
       <c r="T120" s="10"/>
       <c r="U120" s="10"/>
       <c r="V120" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W120" s="12"/>
       <c r="X120" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y120" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z120" s="10" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="Z120" s="10" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AA120" s="10">
         <v>0</v>
       </c>
@@ -14477,10 +14811,13 @@
         <v>51</v>
       </c>
       <c r="AL120" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM120" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM120" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="AN120" s="1"/>
       <c r="AO120" s="1"/>
       <c r="AP120" s="1"/>
@@ -14524,7 +14861,7 @@
         <v>60.4</v>
       </c>
       <c r="L121" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-16.664000000000001</v>
       </c>
       <c r="M121" s="1"/>
@@ -14541,22 +14878,22 @@
       <c r="T121" s="1"/>
       <c r="U121" s="1"/>
       <c r="V121" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>8.7471999999999994</v>
       </c>
       <c r="W121" s="5"/>
       <c r="X121" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y121" s="1">
-        <f t="shared" si="22"/>
-        <v>21.744443936345345</v>
-      </c>
-      <c r="Z121" s="1">
         <f t="shared" si="23"/>
         <v>21.744443936345345</v>
       </c>
+      <c r="Z121" s="1">
+        <f t="shared" si="24"/>
+        <v>21.744443936345345</v>
+      </c>
       <c r="AA121" s="1">
         <v>11.3284</v>
       </c>
@@ -14589,10 +14926,13 @@
       </c>
       <c r="AK121" s="1"/>
       <c r="AL121" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM121" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM121" s="1">
+        <f t="shared" si="26"/>
+        <v>51.424163636363645</v>
+      </c>
       <c r="AN121" s="1"/>
       <c r="AO121" s="1"/>
       <c r="AP121" s="1"/>
@@ -14636,7 +14976,7 @@
         <v>283.2</v>
       </c>
       <c r="L122" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>6.924000000000035</v>
       </c>
       <c r="M122" s="1"/>
@@ -14655,11 +14995,11 @@
       </c>
       <c r="U122" s="1"/>
       <c r="V122" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>58.024800000000006</v>
       </c>
       <c r="W122" s="5">
-        <f t="shared" ref="W122:W129" si="35">12*V122-U122-T122-S122-R122-Q122-P122-O122-F122</f>
+        <f t="shared" ref="W122:W129" si="37">12*V122-U122-T122-S122-R122-Q122-P122-O122-F122</f>
         <v>420.60620000000017</v>
       </c>
       <c r="X122" s="5">
@@ -14667,11 +15007,11 @@
         <v>362.58140000000014</v>
       </c>
       <c r="Y122" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11.000000000000002</v>
       </c>
       <c r="Z122" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4.7512684231569944</v>
       </c>
       <c r="AA122" s="1">
@@ -14706,10 +15046,13 @@
       </c>
       <c r="AK122" s="1"/>
       <c r="AL122" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>363</v>
       </c>
-      <c r="AM122" s="1"/>
+      <c r="AM122" s="1">
+        <f t="shared" si="26"/>
+        <v>239.93543636363643</v>
+      </c>
       <c r="AN122" s="1"/>
       <c r="AO122" s="1"/>
       <c r="AP122" s="1"/>
@@ -14753,7 +15096,7 @@
         <v>83.8</v>
       </c>
       <c r="L123" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>14.871000000000009</v>
       </c>
       <c r="M123" s="1"/>
@@ -14770,23 +15113,23 @@
       <c r="T123" s="1"/>
       <c r="U123" s="1"/>
       <c r="V123" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>19.734200000000001</v>
       </c>
       <c r="W123" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>104.78120000000003</v>
       </c>
       <c r="X123" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>104.78120000000003</v>
       </c>
       <c r="Y123" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12</v>
       </c>
       <c r="Z123" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6.6903750848780286</v>
       </c>
       <c r="AA123" s="1">
@@ -14821,10 +15164,13 @@
       </c>
       <c r="AK123" s="1"/>
       <c r="AL123" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>105</v>
       </c>
-      <c r="AM123" s="1"/>
+      <c r="AM123" s="1">
+        <f t="shared" si="26"/>
+        <v>79.741072727272737</v>
+      </c>
       <c r="AN123" s="1"/>
       <c r="AO123" s="1"/>
       <c r="AP123" s="1"/>
@@ -14868,7 +15214,7 @@
         <v>1001.3339999999999</v>
       </c>
       <c r="L124" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-11.59699999999998</v>
       </c>
       <c r="M124" s="1"/>
@@ -14891,22 +15237,22 @@
       </c>
       <c r="U124" s="1"/>
       <c r="V124" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>197.94739999999999</v>
       </c>
       <c r="W124" s="5"/>
       <c r="X124" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y124" s="1">
-        <f t="shared" si="22"/>
-        <v>12.442652795641672</v>
-      </c>
-      <c r="Z124" s="1">
         <f t="shared" si="23"/>
         <v>12.442652795641672</v>
       </c>
+      <c r="Z124" s="1">
+        <f t="shared" si="24"/>
+        <v>12.442652795641672</v>
+      </c>
       <c r="AA124" s="1">
         <v>193.87379999999999</v>
       </c>
@@ -14941,10 +15287,13 @@
         <v>170</v>
       </c>
       <c r="AL124" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM124" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM124" s="1">
+        <f t="shared" si="26"/>
+        <v>534.71281818181808</v>
+      </c>
       <c r="AN124" s="1"/>
       <c r="AO124" s="1"/>
       <c r="AP124" s="1"/>
@@ -14988,7 +15337,7 @@
         <v>397.7</v>
       </c>
       <c r="L125" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-98.699999999999989</v>
       </c>
       <c r="M125" s="1"/>
@@ -15007,23 +15356,23 @@
       </c>
       <c r="U125" s="1"/>
       <c r="V125" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>59.8</v>
       </c>
       <c r="W125" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>183.99999999999977</v>
       </c>
       <c r="X125" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>183.99999999999977</v>
       </c>
       <c r="Y125" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11.999999999999998</v>
       </c>
       <c r="Z125" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>8.9230769230769251</v>
       </c>
       <c r="AA125" s="1">
@@ -15058,10 +15407,13 @@
       </c>
       <c r="AK125" s="1"/>
       <c r="AL125" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>55</v>
       </c>
-      <c r="AM125" s="1"/>
+      <c r="AM125" s="1">
+        <f t="shared" si="26"/>
+        <v>311.43636363636364</v>
+      </c>
       <c r="AN125" s="1"/>
       <c r="AO125" s="1"/>
       <c r="AP125" s="1"/>
@@ -15105,7 +15457,7 @@
         <v>119</v>
       </c>
       <c r="L126" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-40</v>
       </c>
       <c r="M126" s="1"/>
@@ -15122,23 +15474,23 @@
       <c r="T126" s="1"/>
       <c r="U126" s="1"/>
       <c r="V126" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>15.8</v>
       </c>
       <c r="W126" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>58.600000000000023</v>
       </c>
       <c r="X126" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>58.600000000000023</v>
       </c>
       <c r="Y126" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12.000000000000002</v>
       </c>
       <c r="Z126" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>8.2911392405063289</v>
       </c>
       <c r="AA126" s="1">
@@ -15175,10 +15527,13 @@
         <v>173</v>
       </c>
       <c r="AL126" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>18</v>
       </c>
-      <c r="AM126" s="1"/>
+      <c r="AM126" s="1">
+        <f t="shared" si="26"/>
+        <v>33.727272727272727</v>
+      </c>
       <c r="AN126" s="1"/>
       <c r="AO126" s="1"/>
       <c r="AP126" s="1"/>
@@ -15222,7 +15577,7 @@
         <v>16.100000000000001</v>
       </c>
       <c r="L127" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1.5899999999999999</v>
       </c>
       <c r="M127" s="1"/>
@@ -15239,23 +15594,23 @@
       <c r="T127" s="1"/>
       <c r="U127" s="1"/>
       <c r="V127" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>3.5380000000000003</v>
       </c>
       <c r="W127" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>25.397200000000005</v>
       </c>
       <c r="X127" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>25.397200000000005</v>
       </c>
       <c r="Y127" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12</v>
       </c>
       <c r="Z127" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4.8215941209722999</v>
       </c>
       <c r="AA127" s="1">
@@ -15290,10 +15645,13 @@
       </c>
       <c r="AK127" s="1"/>
       <c r="AL127" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>25</v>
       </c>
-      <c r="AM127" s="1"/>
+      <c r="AM127" s="1">
+        <f t="shared" si="26"/>
+        <v>11.295963636363638</v>
+      </c>
       <c r="AN127" s="1"/>
       <c r="AO127" s="1"/>
       <c r="AP127" s="1"/>
@@ -15337,7 +15695,7 @@
         <v>131</v>
       </c>
       <c r="L128" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-52</v>
       </c>
       <c r="M128" s="1"/>
@@ -15354,22 +15712,22 @@
       <c r="T128" s="1"/>
       <c r="U128" s="1"/>
       <c r="V128" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>15.8</v>
       </c>
       <c r="W128" s="5"/>
       <c r="X128" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y128" s="1">
-        <f t="shared" si="22"/>
-        <v>19.556962025316455</v>
-      </c>
-      <c r="Z128" s="1">
         <f t="shared" si="23"/>
         <v>19.556962025316455</v>
       </c>
+      <c r="Z128" s="1">
+        <f t="shared" si="24"/>
+        <v>19.556962025316455</v>
+      </c>
       <c r="AA128" s="1">
         <v>14.6</v>
       </c>
@@ -15402,10 +15760,13 @@
       </c>
       <c r="AK128" s="1"/>
       <c r="AL128" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM128" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM128" s="1">
+        <f t="shared" si="26"/>
+        <v>144.4545454545455</v>
+      </c>
       <c r="AN128" s="1"/>
       <c r="AO128" s="1"/>
       <c r="AP128" s="1"/>
@@ -15447,7 +15808,7 @@
         <v>86</v>
       </c>
       <c r="L129" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>2</v>
       </c>
       <c r="M129" s="1"/>
@@ -15464,23 +15825,23 @@
       <c r="T129" s="1"/>
       <c r="U129" s="1"/>
       <c r="V129" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>17.600000000000001</v>
       </c>
       <c r="W129" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>93.600000000000023</v>
       </c>
       <c r="X129" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>93.600000000000023</v>
       </c>
       <c r="Y129" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12</v>
       </c>
       <c r="Z129" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6.6818181818181808</v>
       </c>
       <c r="AA129" s="1">
@@ -15515,10 +15876,13 @@
       </c>
       <c r="AK129" s="1"/>
       <c r="AL129" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>11</v>
       </c>
-      <c r="AM129" s="1"/>
+      <c r="AM129" s="1">
+        <f t="shared" si="26"/>
+        <v>52.309090909090905</v>
+      </c>
       <c r="AN129" s="1"/>
       <c r="AO129" s="1"/>
       <c r="AP129" s="1"/>
@@ -15530,7 +15894,7 @@
       <c r="AV129" s="1"/>
     </row>
     <row r="130" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A130" s="13" t="s">
+      <c r="A130" s="1" t="s">
         <v>177</v>
       </c>
       <c r="B130" s="1" t="s">
@@ -15550,7 +15914,7 @@
       <c r="J130" s="1"/>
       <c r="K130" s="1"/>
       <c r="L130" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M130" s="1"/>
@@ -15567,22 +15931,22 @@
       </c>
       <c r="U130" s="1"/>
       <c r="V130" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W130" s="5"/>
       <c r="X130" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y130" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z130" s="1" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="Z130" s="1" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AA130" s="1">
         <v>0</v>
       </c>
@@ -15617,10 +15981,13 @@
         <v>178</v>
       </c>
       <c r="AL130" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM130" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM130" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="AN130" s="1"/>
       <c r="AO130" s="1"/>
       <c r="AP130" s="1"/>
@@ -15632,7 +15999,7 @@
       <c r="AV130" s="1"/>
     </row>
     <row r="131" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A131" s="13" t="s">
+      <c r="A131" s="1" t="s">
         <v>179</v>
       </c>
       <c r="B131" s="1" t="s">
@@ -15652,7 +16019,7 @@
       <c r="J131" s="1"/>
       <c r="K131" s="1"/>
       <c r="L131" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M131" s="1"/>
@@ -15669,22 +16036,22 @@
       </c>
       <c r="U131" s="1"/>
       <c r="V131" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W131" s="5"/>
       <c r="X131" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y131" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z131" s="1" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="Z131" s="1" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AA131" s="1">
         <v>0</v>
       </c>
@@ -15719,10 +16086,13 @@
         <v>178</v>
       </c>
       <c r="AL131" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM131" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM131" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="AN131" s="1"/>
       <c r="AO131" s="1"/>
       <c r="AP131" s="1"/>
@@ -15734,7 +16104,7 @@
       <c r="AV131" s="1"/>
     </row>
     <row r="132" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A132" s="13" t="s">
+      <c r="A132" s="1" t="s">
         <v>180</v>
       </c>
       <c r="B132" s="1" t="s">
@@ -15754,7 +16124,7 @@
       <c r="J132" s="1"/>
       <c r="K132" s="1"/>
       <c r="L132" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="M132" s="1"/>
@@ -15771,22 +16141,22 @@
       </c>
       <c r="U132" s="1"/>
       <c r="V132" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="W132" s="5"/>
       <c r="X132" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Y132" s="1" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z132" s="1" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="Z132" s="1" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AA132" s="1">
         <v>0</v>
       </c>
@@ -15821,10 +16191,13 @@
         <v>178</v>
       </c>
       <c r="AL132" s="1">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AM132" s="1"/>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AM132" s="1">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="AN132" s="1"/>
       <c r="AO132" s="1"/>
       <c r="AP132" s="1"/>
